--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1192,8 +1192,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4"/>
     <row r="5" ht="27.75" customHeight="1" s="19">
       <c r="A5" s="10" t="inlineStr">
         <is>
@@ -1337,11 +1335,15 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
+      <c r="P6" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5).</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="82.8" customHeight="1" s="19">
       <c r="A7" s="13" t="inlineStr">
@@ -1404,11 +1406,15 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O7" s="14" t="n"/>
-      <c r="P7" s="14" t="n"/>
+      <c r="P7" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. Falta la fecha propuesta editable (CA2) y el descarte con motivo de 10 caracteres (CA4).</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="82.8" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -1471,11 +1477,15 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O8" s="12" t="n"/>
-      <c r="P8" s="12" t="n"/>
+      <c r="P8" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2).</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="55.2" customHeight="1" s="19">
       <c r="A9" s="13" t="inlineStr">
@@ -1739,11 +1749,15 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O12" s="12" t="n"/>
-      <c r="P12" s="12" t="n"/>
+      <c r="P12" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: Operación › Cumplimiento (BD/402) mide ocurrencias completadas sobre programadas contra la fecha original, por mes, por plan y por activo (CA1 y CA3). El desglose completo (CA2) tiene completadas y atrasadas; faltan reprogramadas y omitidas por separado.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="55.2" customHeight="1" s="19">
       <c r="A13" s="13" t="inlineStr">
@@ -1940,11 +1954,15 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O15" s="14" t="n"/>
-      <c r="P15" s="14" t="n"/>
+      <c r="P15" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: Centro de carga de datos (Utilidades › Carga de datos): plantilla con ejemplo, revisión sin escribir y carga confirmada para Inventario, Activos y Mantenimiento (BD/334, 335, 368, 473). Cubre CA1, CA3 y CA4. Falta CA2: avisar que el archivo ya se cargó (hoy volver a cargar no duplica porque los códigos actualizan u omiten).</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="82.8" customHeight="1" s="19">
       <c r="A16" s="11" t="inlineStr">
@@ -2007,11 +2025,15 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O16" s="12" t="n"/>
-      <c r="P16" s="12" t="n"/>
+      <c r="P16" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="55.2" customHeight="1" s="19">
       <c r="A17" s="13" t="inlineStr">
@@ -2074,11 +2096,15 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
+      <c r="P17" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo.</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="69" customHeight="1" s="19">
       <c r="A18" s="11" t="inlineStr">
@@ -2141,11 +2167,15 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O18" s="12" t="n"/>
-      <c r="P18" s="12" t="n"/>
+      <c r="P18" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="55.2" customHeight="1" s="19">
       <c r="A19" s="13" t="inlineStr">
@@ -2610,11 +2640,15 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O25" s="14" t="n"/>
-      <c r="P25" s="14" t="n"/>
+      <c r="P25" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 16-10-2026: El historial de cargas guarda cada revisión y carga con archivo, fecha, usuario, módulo y resultado, y permite alertar un problema (CA1). El detalle por registro creado (CA2) queda como resumen por hoja.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -6243,11 +6277,15 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="J6" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="41.4" customHeight="1" s="19">
       <c r="A7" s="11" t="inlineStr">
@@ -6285,11 +6323,15 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
-      <c r="J7" s="12" t="n"/>
+      <c r="J7" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="27.6" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -6327,11 +6369,15 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
-      <c r="J8" s="12" t="n"/>
+      <c r="J8" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="27.6" customHeight="1" s="19">
       <c r="A9" s="11" t="inlineStr">
@@ -6369,11 +6415,15 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12" t="n"/>
+      <c r="J9" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27.6" customHeight="1" s="19">
       <c r="A10" s="11" t="inlineStr">
@@ -6495,11 +6545,15 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
-      <c r="J12" s="12" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -6579,11 +6633,15 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
-      <c r="J14" s="12" t="n"/>
+      <c r="J14" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="41.4" customHeight="1" s="19">
       <c r="A15" s="11" t="inlineStr">
@@ -6747,11 +6805,15 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
-      <c r="J18" s="12" t="n"/>
+      <c r="J18" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="41.4" customHeight="1" s="19">
       <c r="A19" s="11" t="inlineStr">
@@ -6789,11 +6851,15 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12" t="n"/>
+      <c r="J19" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="27.6" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -6831,11 +6897,15 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
-      <c r="J20" s="12" t="n"/>
+      <c r="J20" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="27.6" customHeight="1" s="19">
       <c r="A21" s="11" t="inlineStr">
@@ -6873,11 +6943,15 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12" t="n"/>
+      <c r="J21" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="27.6" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -6915,11 +6989,15 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I22" s="11" t="n"/>
-      <c r="J22" s="12" t="n"/>
+      <c r="J22" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="27.6" customHeight="1" s="19">
       <c r="A23" s="11" t="inlineStr">
@@ -6957,11 +7035,15 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
-      <c r="J23" s="12" t="n"/>
+      <c r="J23" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27.6" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -6999,11 +7081,15 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
-      <c r="J24" s="12" t="n"/>
+      <c r="J24" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="41.4" customHeight="1" s="19">
       <c r="A25" s="11" t="inlineStr">
@@ -7125,11 +7211,15 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I27" s="11" t="n"/>
-      <c r="J27" s="12" t="n"/>
+      <c r="J27" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="41.4" customHeight="1" s="19">
       <c r="A28" s="11" t="inlineStr">
@@ -7167,11 +7257,15 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I28" s="11" t="n"/>
-      <c r="J28" s="12" t="n"/>
+      <c r="J28" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="27.6" customHeight="1" s="19">
       <c r="A29" s="11" t="inlineStr">
@@ -7209,11 +7303,15 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
-      <c r="J29" s="12" t="n"/>
+      <c r="J29" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="41.4" customHeight="1" s="19">
       <c r="A30" s="11" t="inlineStr">
@@ -7251,11 +7349,15 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
-      <c r="J30" s="12" t="n"/>
+      <c r="J30" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="27.6" customHeight="1" s="19">
       <c r="A31" s="11" t="inlineStr">
@@ -7377,11 +7479,15 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
-      <c r="J33" s="12" t="n"/>
+      <c r="J33" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="27.6" customHeight="1" s="19">
       <c r="A34" s="11" t="inlineStr">
@@ -7461,11 +7567,15 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
-      <c r="J35" s="12" t="n"/>
+      <c r="J35" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="41.4" customHeight="1" s="19">
       <c r="A36" s="11" t="inlineStr">
@@ -8931,11 +9041,15 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
-      <c r="J70" s="12" t="n"/>
+      <c r="J70" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="27.6" customHeight="1" s="19">
       <c r="A71" s="11" t="inlineStr">
@@ -8973,11 +9087,15 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
-      <c r="J71" s="12" t="n"/>
+      <c r="J71" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="27.6" customHeight="1" s="19">
       <c r="A72" s="11" t="inlineStr">
@@ -9015,11 +9133,15 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
-      <c r="J72" s="12" t="n"/>
+      <c r="J72" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="27.6" customHeight="1" s="19">
       <c r="A73" s="11" t="inlineStr">
@@ -9057,11 +9179,15 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
-      <c r="J73" s="12" t="n"/>
+      <c r="J73" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="55.2" customHeight="1" s="19">
       <c r="A74" s="11" t="inlineStr">
@@ -9099,11 +9225,15 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
-      <c r="J74" s="12" t="n"/>
+      <c r="J74" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="41.4" customHeight="1" s="19">
       <c r="A75" s="11" t="inlineStr">
@@ -9141,11 +9271,15 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
-      <c r="J75" s="12" t="n"/>
+      <c r="J75" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="41.4" customHeight="1" s="19">
       <c r="A76" s="11" t="inlineStr">
@@ -10023,11 +10157,15 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I96" s="11" t="n"/>
-      <c r="J96" s="12" t="n"/>
+      <c r="J96" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="27.6" customHeight="1" s="19">
       <c r="A97" s="11" t="inlineStr">
@@ -10065,11 +10203,15 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I97" s="11" t="n"/>
-      <c r="J97" s="12" t="n"/>
+      <c r="J97" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="41.4" customHeight="1" s="19">
       <c r="A98" s="11" t="inlineStr">
@@ -10107,11 +10249,15 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I98" s="11" t="n"/>
-      <c r="J98" s="12" t="n"/>
+      <c r="J98" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="41.4" customHeight="1" s="19">
       <c r="A99" s="11" t="inlineStr">
@@ -10149,11 +10295,15 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I99" s="11" t="n"/>
-      <c r="J99" s="12" t="n"/>
+      <c r="J99" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="100" ht="27.6" customHeight="1" s="19">
       <c r="A100" s="11" t="inlineStr">
@@ -10191,11 +10341,15 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I100" s="11" t="n"/>
-      <c r="J100" s="12" t="n"/>
+      <c r="J100" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="27.6" customHeight="1" s="19">
       <c r="A101" s="11" t="inlineStr">
@@ -10233,11 +10387,15 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I101" s="11" t="n"/>
-      <c r="J101" s="12" t="n"/>
+      <c r="J101" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="27.6" customHeight="1" s="19">
       <c r="A102" s="11" t="inlineStr">
@@ -10275,11 +10433,15 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I102" s="11" t="n"/>
-      <c r="J102" s="12" t="n"/>
+      <c r="J102" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="27.6" customHeight="1" s="19">
       <c r="A103" s="11" t="inlineStr">
@@ -10443,11 +10605,15 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
-      <c r="J106" s="12" t="n"/>
+      <c r="J106" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="41.4" customHeight="1" s="19">
       <c r="A107" s="11" t="inlineStr">
@@ -10485,11 +10651,15 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
-      <c r="J107" s="12" t="n"/>
+      <c r="J107" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="27.6" customHeight="1" s="19">
       <c r="A108" s="11" t="inlineStr">
@@ -10527,11 +10697,15 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
-      <c r="J108" s="12" t="n"/>
+      <c r="J108" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="41.4" customHeight="1" s="19">
       <c r="A109" s="11" t="inlineStr">
@@ -10569,11 +10743,15 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
-      <c r="J109" s="12" t="n"/>
+      <c r="J109" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="41.4" customHeight="1" s="19">
       <c r="A110" s="11" t="inlineStr">
@@ -10695,11 +10873,15 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
-      <c r="J112" s="12" t="n"/>
+      <c r="J112" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="27.6" customHeight="1" s="19">
       <c r="A113" s="11" t="inlineStr">
@@ -10779,11 +10961,15 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
-      <c r="J114" s="12" t="n"/>
+      <c r="J114" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="27.6" customHeight="1" s="19">
       <c r="A115" s="11" t="inlineStr">
@@ -10905,11 +11091,15 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
-      <c r="J117" s="12" t="n"/>
+      <c r="J117" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="41.4" customHeight="1" s="19">
       <c r="A118" s="11" t="inlineStr">
@@ -10947,11 +11137,15 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
-      <c r="J118" s="12" t="n"/>
+      <c r="J118" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="41.4" customHeight="1" s="19">
       <c r="A119" s="11" t="inlineStr">
@@ -10989,11 +11183,15 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I119" s="11" t="n"/>
-      <c r="J119" s="12" t="n"/>
+      <c r="J119" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="27.6" customHeight="1" s="19">
       <c r="A120" s="11" t="inlineStr">
@@ -11031,11 +11229,15 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
-      <c r="J120" s="12" t="n"/>
+      <c r="J120" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="27.6" customHeight="1" s="19">
       <c r="A121" s="11" t="inlineStr">
@@ -11073,11 +11275,15 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
-      <c r="J121" s="12" t="n"/>
+      <c r="J121" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="41.4" customHeight="1" s="19">
       <c r="A122" s="11" t="inlineStr">
@@ -11115,11 +11321,15 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
-      <c r="J122" s="12" t="n"/>
+      <c r="J122" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="27.6" customHeight="1" s="19">
       <c r="A123" s="11" t="inlineStr">
@@ -11157,11 +11367,15 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
-      <c r="J123" s="12" t="n"/>
+      <c r="J123" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="27.6" customHeight="1" s="19">
       <c r="A124" s="11" t="inlineStr">
@@ -11325,11 +11539,15 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
-      <c r="J127" s="12" t="n"/>
+      <c r="J127" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="41.4" customHeight="1" s="19">
       <c r="A128" s="11" t="inlineStr">
@@ -11367,11 +11585,15 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
-      <c r="J128" s="12" t="n"/>
+      <c r="J128" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="55.2" customHeight="1" s="19">
       <c r="A129" s="11" t="inlineStr">
@@ -11409,11 +11631,15 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="n"/>
+      <c r="J129" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="41.4" customHeight="1" s="19">
       <c r="A130" s="11" t="inlineStr">
@@ -11451,11 +11677,15 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I130" s="11" t="n"/>
-      <c r="J130" s="12" t="n"/>
+      <c r="J130" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="41.4" customHeight="1" s="19">
       <c r="A131" s="11" t="inlineStr">
@@ -11493,11 +11723,15 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
-      <c r="J131" s="12" t="n"/>
+      <c r="J131" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="41.4" customHeight="1" s="19">
       <c r="A132" s="11" t="inlineStr">
@@ -11535,11 +11769,15 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
-      <c r="J132" s="12" t="n"/>
+      <c r="J132" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="41.4" customHeight="1" s="19">
       <c r="A133" s="11" t="inlineStr">
@@ -11577,11 +11815,15 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="n"/>
+      <c r="J133" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="27.6" customHeight="1" s="19">
       <c r="A134" s="11" t="inlineStr">
@@ -14557,11 +14799,15 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I202" s="11" t="n"/>
-      <c r="J202" s="12" t="n"/>
+      <c r="J202" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="27.6" customHeight="1" s="19">
       <c r="A203" s="11" t="inlineStr">
@@ -14599,11 +14845,15 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I203" s="11" t="n"/>
-      <c r="J203" s="12" t="n"/>
+      <c r="J203" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="41.4" customHeight="1" s="19">
       <c r="A204" s="11" t="inlineStr">
@@ -14641,11 +14891,15 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I204" s="11" t="n"/>
-      <c r="J204" s="12" t="n"/>
+      <c r="J204" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="55.2" customHeight="1" s="19">
       <c r="A205" s="11" t="inlineStr">
@@ -14683,11 +14937,15 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I205" s="11" t="n"/>
-      <c r="J205" s="12" t="n"/>
+      <c r="J205" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="41.4" customHeight="1" s="19">
       <c r="A206" s="11" t="inlineStr">
@@ -14725,11 +14983,15 @@
       </c>
       <c r="H206" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I206" s="11" t="n"/>
-      <c r="J206" s="12" t="n"/>
+      <c r="J206" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="41.4" customHeight="1" s="19">
       <c r="A207" s="11" t="inlineStr">
@@ -14767,11 +15029,15 @@
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I207" s="11" t="n"/>
-      <c r="J207" s="12" t="n"/>
+      <c r="J207" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="41.4" customHeight="1" s="19">
       <c r="A208" s="11" t="inlineStr">
@@ -30090,7 +30356,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30152,7 +30418,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30373,7 +30639,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30436,7 +30702,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30467,7 +30733,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30499,7 +30765,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30562,7 +30828,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30594,7 +30860,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30689,7 +30955,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30721,7 +30987,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30784,7 +31050,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31383,7 +31649,7 @@
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1341,7 +1341,7 @@
       <c r="O6" s="12" t="n"/>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5).</t>
+          <t>Avance web al 17-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5).</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       <c r="O7" s="14" t="n"/>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. Falta la fecha propuesta editable (CA2) y el descarte con motivo de 10 caracteres (CA4).</t>
+          <t>Avance web al 17-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. La fecha programada propuesta (CA2) se dejó fuera a propósito: BD/117 decide que programar es una decisión de planificación con dotación y repuestos a la vista. El descarte pide motivo de una lista más detalle opcional, no 10 caracteres (CA4).</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
       <c r="O8" s="12" t="n"/>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2).</t>
+          <t>Avance web al 17-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2).</t>
         </is>
       </c>
     </row>
@@ -1548,11 +1548,19 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="n"/>
-      <c r="P9" s="14" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P9" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Mantenimiento › Indicadores › Tablero (BD/474, WsIndicadores): cumplimiento, disponibilidad, tiempo medio entre fallas, tiempo medio de reparación y órdenes pendientes de cierre con su variación contra el período anterior (CA1); filtros de planta, área, equipo y fechas que recalculan todo (CA2); cada indicador abre su detalle en un cajón (CA3).</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="69" customHeight="1" s="19">
       <c r="A10" s="11" t="inlineStr">
@@ -1682,11 +1690,19 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="n"/>
-      <c r="P11" s="14" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P11" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Pantalla SIGMA AI › Desempeño › «Por evaluar» (View/SigmaAI/Desempeno.aspx, WsAiDesempeno, BD/475): lista las predicciones con el horizonte vencido sin evaluar (CA3), registra si el evento ocurrió y cuándo con el error en días calculado por el SP (CA1) y clasifica «acierto con intervención» aparte de la falsa alarma (CA2).</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="82.8" customHeight="1" s="19">
       <c r="A12" s="11" t="inlineStr">
@@ -1755,7 +1771,7 @@
       <c r="O12" s="12" t="n"/>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: Operación › Cumplimiento (BD/402) mide ocurrencias completadas sobre programadas contra la fecha original, por mes, por plan y por activo (CA1 y CA3). El desglose completo (CA2) tiene completadas y atrasadas; faltan reprogramadas y omitidas por separado.</t>
+          <t>Avance web al 17-10-2026: El tablero y Operación › Cumplimiento miden hechas sobre vencidas contra la fecha original (CA1) y ordenan los equipos del peor al mejor (CA3). El desglose completo (CA2) distingue hechas y vencidas; faltan reprogramadas y omitidas por separado.</t>
         </is>
       </c>
     </row>
@@ -1820,11 +1836,19 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="n"/>
-      <c r="P13" s="14" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P13" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Tablero e indicadores (BD/474): disponibilidad con la indisponibilidad no planificada descontada y la planificada aparte (CA1); tiempo medio entre fallas con aviso cuando hay menos de 3 fallas (CA2); tiempo medio de reparación sobre las correctivas cerradas (CA3).</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="55.2" customHeight="1" s="19">
       <c r="A14" s="11" t="inlineStr">
@@ -1887,11 +1911,19 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="O14" s="12" t="n"/>
-      <c r="P14" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O14" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
+      <c r="P14" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Mantenimiento › Indicadores › Costos (BD/474): repuestos, mano de obra y servicios por equipo y siempre por moneda (CA1); por centro de costo con el de sus dependientes (CA2, probado con un árbol de prueba revertido); comparación con el período anterior en variación absoluta y porcentual (CA3).</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="69" customHeight="1" s="19">
       <c r="A15" s="13" t="inlineStr">
@@ -1954,13 +1986,17 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: Centro de carga de datos (Utilidades › Carga de datos): plantilla con ejemplo, revisión sin escribir y carga confirmada para Inventario, Activos y Mantenimiento (BD/334, 335, 368, 473). Cubre CA1, CA3 y CA4. Falta CA2: avisar que el archivo ya se cargó (hoy volver a cargar no duplica porque los códigos actualizan u omiten).</t>
+          <t>Avance web al 17-10-2026: Centro de carga de datos (BD/334, 335, 368, 473, 476): revisión sin escribir (CA1), aviso de que la planilla ya se procesó, con fecha y usuario, gracias a la huella SHA-256 del archivo (CA2), carga confirmada (CA3) y plantilla con ejemplo (CA4).</t>
         </is>
       </c>
     </row>
@@ -2031,7 +2067,7 @@
       <c r="O16" s="12" t="n"/>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación.</t>
+          <t>Avance web al 17-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2138,7 @@
       <c r="O17" s="14" t="n"/>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo.</t>
+          <t>Avance web al 17-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo.</t>
         </is>
       </c>
     </row>
@@ -2173,7 +2209,7 @@
       <c r="O18" s="12" t="n"/>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo.</t>
+          <t>Avance web al 17-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo.</t>
         </is>
       </c>
     </row>
@@ -2439,11 +2475,15 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O22" s="12" t="n"/>
-      <c r="P22" s="12" t="n"/>
+      <c r="P22" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Excel con los mismos filtros de la pantalla y encabezado de cliente, período y filtros (CA1) e impresión con el pie del cliente (CA2), para el tablero, el detalle de cada indicador y los costos. Falta ofrecerlos en los demás listados de SIGMA (Operación, órdenes, activos).</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="69" customHeight="1" s="19">
       <c r="A23" s="13" t="inlineStr">
@@ -2506,11 +2546,15 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
+      <c r="P23" s="14" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Centro de SIGMA AI › Fotos de terreno: cada detección se presenta «por confirmar» y no como confirmada hasta que una persona la confirma o corrige (CA3 y CA4), y esa decisión alimenta el dataset. Falta la cola de análisis con prioridad (CA1) y dibujar las zonas detectadas sobre la imagen (CA2).</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="82.8" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -2573,11 +2617,15 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="O24" s="12" t="n"/>
-      <c r="P24" s="12" t="n"/>
+      <c r="P24" s="12" t="inlineStr">
+        <is>
+          <t>Avance web al 17-10-2026: Pestaña «Desempeño» (BD/475): por versión y mes, predicciones, evaluadas, aciertos, falsas alarmas y aciertos con intervención aparte (CA1); la versión queda «candidata a reentrenamiento» si la precisión cae bajo la de referencia con al menos 5 evaluadas (CA2). Falta la desviación de los datos de entrada (CA3): no se guarda la distribución del entrenamiento.</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="69" customHeight="1" s="19">
       <c r="A25" s="13" t="inlineStr">
@@ -2640,13 +2688,17 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 16-10-2026: El historial de cargas guarda cada revisión y carga con archivo, fecha, usuario, módulo y resultado, y permite alertar un problema (CA1). El detalle por registro creado (CA2) queda como resumen por hoja.</t>
+          <t>Avance web al 17-10-2026: El historial guarda cada revisión y carga con archivo, fecha, usuario, módulo y resultado (CA1); al abrir una carga se ve el resultado por hoja, con filas, creadas, actualizadas, omitidas y errores (CA2).</t>
         </is>
       </c>
     </row>
@@ -7697,11 +7749,17 @@
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="n"/>
-      <c r="J38" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="41.4" customHeight="1" s="19">
       <c r="A39" s="11" t="inlineStr">
@@ -7739,11 +7797,17 @@
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="n"/>
-      <c r="J39" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J39" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="41.4" customHeight="1" s="19">
       <c r="A40" s="11" t="inlineStr">
@@ -7781,11 +7845,17 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="n"/>
-      <c r="J40" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J40" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="41.4" customHeight="1" s="19">
       <c r="A41" s="11" t="inlineStr">
@@ -7823,11 +7893,17 @@
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="n"/>
-      <c r="J41" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="27.6" customHeight="1" s="19">
       <c r="A42" s="11" t="inlineStr">
@@ -7865,11 +7941,17 @@
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="n"/>
-      <c r="J42" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J42" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="27.6" customHeight="1" s="19">
       <c r="A43" s="11" t="inlineStr">
@@ -7907,11 +7989,17 @@
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="n"/>
-      <c r="J43" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="27.6" customHeight="1" s="19">
       <c r="A44" s="11" t="inlineStr">
@@ -7949,11 +8037,17 @@
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="n"/>
-      <c r="J44" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="27.6" customHeight="1" s="19">
       <c r="A45" s="11" t="inlineStr">
@@ -7991,11 +8085,17 @@
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="n"/>
-      <c r="J45" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27.6" customHeight="1" s="19">
       <c r="A46" s="11" t="inlineStr">
@@ -8033,11 +8133,17 @@
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="n"/>
-      <c r="J46" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J46" s="12" t="inlineStr">
+        <is>
+          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="55.2" customHeight="1" s="19">
       <c r="A47" s="11" t="inlineStr">
@@ -8621,11 +8727,17 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n"/>
-      <c r="J60" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J60" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="41.4" customHeight="1" s="19">
       <c r="A61" s="11" t="inlineStr">
@@ -8663,11 +8775,17 @@
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="n"/>
-      <c r="J61" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J61" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="41.4" customHeight="1" s="19">
       <c r="A62" s="11" t="inlineStr">
@@ -8705,11 +8823,17 @@
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="n"/>
-      <c r="J62" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J62" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="27.6" customHeight="1" s="19">
       <c r="A63" s="11" t="inlineStr">
@@ -8747,11 +8871,17 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="n"/>
-      <c r="J63" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J63" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="27.6" customHeight="1" s="19">
       <c r="A64" s="11" t="inlineStr">
@@ -8789,11 +8919,17 @@
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="n"/>
-      <c r="J64" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J64" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="41.4" customHeight="1" s="19">
       <c r="A65" s="11" t="inlineStr">
@@ -8831,11 +8967,17 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="n"/>
-      <c r="J65" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J65" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="27.6" customHeight="1" s="19">
       <c r="A66" s="11" t="inlineStr">
@@ -8873,11 +9015,17 @@
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="n"/>
-      <c r="J66" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J66" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="27.6" customHeight="1" s="19">
       <c r="A67" s="11" t="inlineStr">
@@ -8915,11 +9063,17 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="n"/>
-      <c r="J67" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J67" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="27.6" customHeight="1" s="19">
       <c r="A68" s="11" t="inlineStr">
@@ -8957,11 +9111,17 @@
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="n"/>
-      <c r="J68" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J68" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="41.4" customHeight="1" s="19">
       <c r="A69" s="11" t="inlineStr">
@@ -8999,11 +9159,17 @@
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="n"/>
-      <c r="J69" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J69" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="27.6" customHeight="1" s="19">
       <c r="A70" s="11" t="inlineStr">
@@ -9401,11 +9567,17 @@
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n"/>
-      <c r="J78" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="27.6" customHeight="1" s="19">
       <c r="A79" s="11" t="inlineStr">
@@ -9443,11 +9615,17 @@
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="n"/>
-      <c r="J79" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27.6" customHeight="1" s="19">
       <c r="A80" s="11" t="inlineStr">
@@ -9485,11 +9663,17 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n"/>
-      <c r="J80" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="27.6" customHeight="1" s="19">
       <c r="A81" s="11" t="inlineStr">
@@ -9527,11 +9711,17 @@
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="n"/>
-      <c r="J81" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J81" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="27.6" customHeight="1" s="19">
       <c r="A82" s="11" t="inlineStr">
@@ -9569,11 +9759,17 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="n"/>
-      <c r="J82" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J82" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="27.6" customHeight="1" s="19">
       <c r="A83" s="11" t="inlineStr">
@@ -9611,11 +9807,17 @@
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="n"/>
-      <c r="J83" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J83" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="55.2" customHeight="1" s="19">
       <c r="A84" s="11" t="inlineStr">
@@ -9653,11 +9855,17 @@
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="n"/>
-      <c r="J84" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J84" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="41.4" customHeight="1" s="19">
       <c r="A85" s="11" t="inlineStr">
@@ -9695,11 +9903,17 @@
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="n"/>
-      <c r="J85" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J85" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="41.4" customHeight="1" s="19">
       <c r="A86" s="11" t="inlineStr">
@@ -9737,11 +9951,17 @@
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="n"/>
-      <c r="J86" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J86" s="12" t="inlineStr">
+        <is>
+          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="41.4" customHeight="1" s="19">
       <c r="A87" s="11" t="inlineStr">
@@ -9779,11 +9999,17 @@
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n"/>
-      <c r="J87" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="41.4" customHeight="1" s="19">
       <c r="A88" s="11" t="inlineStr">
@@ -9821,11 +10047,17 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="n"/>
-      <c r="J88" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="89" ht="27.6" customHeight="1" s="19">
       <c r="A89" s="11" t="inlineStr">
@@ -9863,11 +10095,17 @@
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="n"/>
-      <c r="J89" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J89" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="27.6" customHeight="1" s="19">
       <c r="A90" s="11" t="inlineStr">
@@ -9905,11 +10143,17 @@
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="n"/>
-      <c r="J90" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J90" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="27.6" customHeight="1" s="19">
       <c r="A91" s="11" t="inlineStr">
@@ -9947,11 +10191,17 @@
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n"/>
-      <c r="J91" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J91" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="27.6" customHeight="1" s="19">
       <c r="A92" s="11" t="inlineStr">
@@ -9989,11 +10239,17 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="n"/>
-      <c r="J92" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J92" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="27.6" customHeight="1" s="19">
       <c r="A93" s="11" t="inlineStr">
@@ -10031,11 +10287,17 @@
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="n"/>
-      <c r="J93" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="J93" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="55.2" customHeight="1" s="19">
       <c r="A94" s="11" t="inlineStr">
@@ -10073,11 +10335,17 @@
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="n"/>
-      <c r="J94" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J94" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="41.4" customHeight="1" s="19">
       <c r="A95" s="11" t="inlineStr">
@@ -10115,11 +10383,17 @@
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="n"/>
-      <c r="J95" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J95" s="12" t="inlineStr">
+        <is>
+          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="41.4" customHeight="1" s="19">
       <c r="A96" s="11" t="inlineStr">
@@ -10157,13 +10431,15 @@
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10203,13 +10479,15 @@
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J97" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10249,13 +10527,15 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10295,13 +10575,15 @@
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J99" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10341,13 +10623,15 @@
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="n">
+        <v>1.25</v>
+      </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10387,13 +10671,15 @@
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="n">
+        <v>4</v>
+      </c>
       <c r="J101" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10433,13 +10719,15 @@
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="n">
+        <v>1.5</v>
+      </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -10479,11 +10767,17 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="n"/>
-      <c r="J103" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J103" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="104" ht="27.6" customHeight="1" s="19">
       <c r="A104" s="11" t="inlineStr">
@@ -10521,11 +10815,17 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="n"/>
-      <c r="J104" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J104" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="55.2" customHeight="1" s="19">
       <c r="A105" s="11" t="inlineStr">
@@ -10563,11 +10863,17 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="n"/>
-      <c r="J105" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J105" s="12" t="inlineStr">
+        <is>
+          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="41.4" customHeight="1" s="19">
       <c r="A106" s="11" t="inlineStr">
@@ -13665,11 +13971,15 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
-      <c r="J175" s="12" t="n"/>
+      <c r="J175" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="27.6" customHeight="1" s="19">
       <c r="A176" s="11" t="inlineStr">
@@ -13707,11 +14017,15 @@
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
-      <c r="J176" s="12" t="n"/>
+      <c r="J176" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="27.6" customHeight="1" s="19">
       <c r="A177" s="11" t="inlineStr">
@@ -13749,11 +14063,15 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
-      <c r="J177" s="12" t="n"/>
+      <c r="J177" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="27.6" customHeight="1" s="19">
       <c r="A178" s="11" t="inlineStr">
@@ -13791,11 +14109,15 @@
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
-      <c r="J178" s="12" t="n"/>
+      <c r="J178" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="27.6" customHeight="1" s="19">
       <c r="A179" s="11" t="inlineStr">
@@ -13833,11 +14155,15 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I179" s="11" t="n"/>
-      <c r="J179" s="12" t="n"/>
+      <c r="J179" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="41.4" customHeight="1" s="19">
       <c r="A180" s="11" t="inlineStr">
@@ -13875,11 +14201,15 @@
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I180" s="11" t="n"/>
-      <c r="J180" s="12" t="n"/>
+      <c r="J180" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="55.2" customHeight="1" s="19">
       <c r="A181" s="11" t="inlineStr">
@@ -13917,11 +14247,15 @@
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I181" s="11" t="n"/>
-      <c r="J181" s="12" t="n"/>
+      <c r="J181" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="41.4" customHeight="1" s="19">
       <c r="A182" s="11" t="inlineStr">
@@ -14043,11 +14377,15 @@
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
-      <c r="J184" s="12" t="n"/>
+      <c r="J184" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="41.4" customHeight="1" s="19">
       <c r="A185" s="11" t="inlineStr">
@@ -14085,11 +14423,15 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
-      <c r="J185" s="12" t="n"/>
+      <c r="J185" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="41.4" customHeight="1" s="19">
       <c r="A186" s="11" t="inlineStr">
@@ -14127,11 +14469,15 @@
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
-      <c r="J186" s="12" t="n"/>
+      <c r="J186" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="27.6" customHeight="1" s="19">
       <c r="A187" s="11" t="inlineStr">
@@ -14169,11 +14515,15 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
-      <c r="J187" s="12" t="n"/>
+      <c r="J187" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="27.6" customHeight="1" s="19">
       <c r="A188" s="11" t="inlineStr">
@@ -14211,11 +14561,15 @@
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
-      <c r="J188" s="12" t="n"/>
+      <c r="J188" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="27.6" customHeight="1" s="19">
       <c r="A189" s="11" t="inlineStr">
@@ -14253,11 +14607,15 @@
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
-      <c r="J189" s="12" t="n"/>
+      <c r="J189" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="27.6" customHeight="1" s="19">
       <c r="A190" s="11" t="inlineStr">
@@ -14421,11 +14779,15 @@
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
-      <c r="J193" s="12" t="n"/>
+      <c r="J193" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="41.4" customHeight="1" s="19">
       <c r="A194" s="11" t="inlineStr">
@@ -14463,11 +14825,15 @@
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
-      <c r="J194" s="12" t="n"/>
+      <c r="J194" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="41.4" customHeight="1" s="19">
       <c r="A195" s="11" t="inlineStr">
@@ -14505,11 +14871,15 @@
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
-      <c r="J195" s="12" t="n"/>
+      <c r="J195" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="27.6" customHeight="1" s="19">
       <c r="A196" s="11" t="inlineStr">
@@ -14547,11 +14917,15 @@
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
-      <c r="J196" s="12" t="n"/>
+      <c r="J196" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="41.4" customHeight="1" s="19">
       <c r="A197" s="11" t="inlineStr">
@@ -14589,11 +14963,15 @@
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
-      <c r="J197" s="12" t="n"/>
+      <c r="J197" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="41.4" customHeight="1" s="19">
       <c r="A198" s="11" t="inlineStr">
@@ -14631,11 +15009,15 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
+          <t>En revisión</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
-      <c r="J198" s="12" t="n"/>
+      <c r="J198" s="12" t="inlineStr">
+        <is>
+          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="27.6" customHeight="1" s="19">
       <c r="A199" s="11" t="inlineStr">
@@ -14799,13 +15181,15 @@
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I202" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J202" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -14845,13 +15229,15 @@
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I203" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J203" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -14891,13 +15277,15 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I204" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I204" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="J204" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -14937,13 +15325,15 @@
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I205" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J205" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -14983,13 +15373,15 @@
       </c>
       <c r="H206" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I206" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="n">
+        <v>0.75</v>
+      </c>
       <c r="J206" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -15029,13 +15421,15 @@
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
-        </is>
-      </c>
-      <c r="I207" s="11" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="n">
+        <v>0.25</v>
+      </c>
       <c r="J207" s="12" t="inlineStr">
         <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
         </is>
       </c>
     </row>
@@ -15075,11 +15469,17 @@
       </c>
       <c r="H208" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I208" s="11" t="n"/>
-      <c r="J208" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J208" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="41.4" customHeight="1" s="19">
       <c r="A209" s="11" t="inlineStr">
@@ -15117,11 +15517,17 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>Por hacer</t>
-        </is>
-      </c>
-      <c r="I209" s="11" t="n"/>
-      <c r="J209" s="12" t="n"/>
+          <t>Terminada</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J209" s="12" t="inlineStr">
+        <is>
+          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="27.6" customHeight="1" s="19">
       <c r="A210" s="11" t="inlineStr">
@@ -29935,7 +30341,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -29966,7 +30372,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -29997,7 +30403,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30258,7 +30664,7 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30293,7 +30699,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30324,7 +30730,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30450,7 +30856,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30482,7 +30888,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30513,7 +30919,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30545,7 +30951,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30576,7 +30982,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30607,7 +31013,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -30670,7 +31076,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31367,7 +31773,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31398,7 +31804,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31493,7 +31899,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31524,7 +31930,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31556,7 +31962,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31587,7 +31993,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -31680,7 +32086,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1338,10 +1338,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O6" s="12" t="n"/>
+      <c r="O6" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5).</t>
+          <t>Avance web al 17-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1409,10 +1413,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O7" s="14" t="n"/>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. La fecha programada propuesta (CA2) se dejó fuera a propósito: BD/117 decide que programar es una decisión de planificación con dotación y repuestos a la vista. El descarte pide motivo de una lista más detalle opcional, no 10 caracteres (CA4).</t>
+          <t>Avance web al 17-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. La fecha programada propuesta (CA2) se dejó fuera a propósito: BD/117 decide que programar es una decisión de planificación con dotación y repuestos a la vista. El descarte pide motivo de una lista más detalle opcional, no 10 caracteres (CA4). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1480,10 +1488,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O8" s="12" t="n"/>
+      <c r="O8" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2).</t>
+          <t>Avance web al 17-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1626,8 +1638,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O10" s="12" t="n"/>
-      <c r="P10" s="12" t="n"/>
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="55.2" customHeight="1" s="19">
       <c r="A11" s="13" t="inlineStr">
@@ -1768,10 +1788,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O12" s="12" t="n"/>
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El tablero y Operación › Cumplimiento miden hechas sobre vencidas contra la fecha original (CA1) y ordenan los equipos del peor al mejor (CA3). El desglose completo (CA2) distingue hechas y vencidas; faltan reprogramadas y omitidas por separado.</t>
+          <t>Avance web al 17-10-2026: El tablero y Operación › Cumplimiento miden hechas sobre vencidas contra la fecha original (CA1) y ordenan los equipos del peor al mejor (CA3). El desglose completo (CA2) distingue hechas y vencidas; faltan reprogramadas y omitidas por separado. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2064,10 +2088,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O16" s="12" t="n"/>
+      <c r="O16" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación.</t>
+          <t>Avance web al 17-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2135,10 +2163,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O17" s="14" t="n"/>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo.</t>
+          <t>Avance web al 17-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2206,10 +2238,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O18" s="12" t="n"/>
+      <c r="O18" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo.</t>
+          <t>Avance web al 17-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2277,8 +2313,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P19" s="14" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="69" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -2344,8 +2388,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O20" s="12" t="n"/>
-      <c r="P20" s="12" t="n"/>
+      <c r="O20" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P20" s="12" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="69" customHeight="1" s="19">
       <c r="A21" s="13" t="inlineStr">
@@ -2411,8 +2463,16 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
+      <c r="P21" s="14" t="inlineStr">
+        <is>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="69" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -2478,10 +2538,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O22" s="12" t="n"/>
+      <c r="O22" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Excel con los mismos filtros de la pantalla y encabezado de cliente, período y filtros (CA1) e impresión con el pie del cliente (CA2), para el tablero, el detalle de cada indicador y los costos. Falta ofrecerlos en los demás listados de SIGMA (Operación, órdenes, activos).</t>
+          <t>Avance web al 17-10-2026: Excel con los mismos filtros de la pantalla y encabezado de cliente, período y filtros (CA1) e impresión con el pie del cliente (CA2), para el tablero, el detalle de cada indicador y los costos. Falta ofrecerlos en los demás listados de SIGMA (Operación, órdenes, activos). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2549,10 +2613,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O23" s="14" t="n"/>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Centro de SIGMA AI › Fotos de terreno: cada detección se presenta «por confirmar» y no como confirmada hasta que una persona la confirma o corrige (CA3 y CA4), y esa decisión alimenta el dataset. Falta la cola de análisis con prioridad (CA1) y dibujar las zonas detectadas sobre la imagen (CA2).</t>
+          <t>Avance web al 17-10-2026: Centro de SIGMA AI › Fotos de terreno: cada detección se presenta «por confirmar» y no como confirmada hasta que una persona la confirma o corrige (CA3 y CA4), y esa decisión alimenta el dataset. Falta la cola de análisis con prioridad (CA1) y dibujar las zonas detectadas sobre la imagen (CA2). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2620,10 +2688,14 @@
           <t>En revisión</t>
         </is>
       </c>
-      <c r="O24" s="12" t="n"/>
+      <c r="O24" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Pestaña «Desempeño» (BD/475): por versión y mes, predicciones, evaluadas, aciertos, falsas alarmas y aciertos con intervención aparte (CA1); la versión queda «candidata a reentrenamiento» si la precisión cae bajo la de referencia con al menos 5 evaluadas (CA2). Falta la desviación de los datos de entrada (CA3): no se guarda la distribución del entrenamiento.</t>
+          <t>Avance web al 17-10-2026: Pestaña «Desempeño» (BD/475): por versión y mes, predicciones, evaluadas, aciertos, falsas alarmas y aciertos con intervención aparte (CA1); la versión queda «candidata a reentrenamiento» si la precisión cae bajo la de referencia con al menos 5 evaluadas (CA2). Falta la desviación de los datos de entrada (CA3): no se guarda la distribución del entrenamiento. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2766,10 +2838,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O26" s="12" t="n"/>
+      <c r="O26" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P26" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2837,10 +2913,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O27" s="12" t="n"/>
+      <c r="O27" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P27" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2908,10 +2988,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O28" s="12" t="n"/>
+      <c r="O28" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P28" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2979,10 +3063,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O29" s="12" t="n"/>
+      <c r="O29" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P29" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3050,10 +3138,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O30" s="12" t="n"/>
+      <c r="O30" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P30" s="12" t="inlineStr">
         <is>
-          <t>Parte móvil + SMTP (T-6301). La historia web sigue en el Sprint 1. Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Parte móvil + SMTP (T-6301). La historia web sigue en el Sprint 1. Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3121,10 +3213,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O31" s="12" t="n"/>
+      <c r="O31" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P31" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 1 (Sprint Review 1). La parte web sigue en el Sprint 1; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3192,10 +3288,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O32" s="12" t="n"/>
+      <c r="O32" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P32" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3263,10 +3363,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O33" s="12" t="n"/>
+      <c r="O33" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P33" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3334,10 +3438,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O34" s="12" t="n"/>
+      <c r="O34" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P34" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3405,10 +3513,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O35" s="12" t="n"/>
+      <c r="O35" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P35" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3476,10 +3588,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O36" s="12" t="n"/>
+      <c r="O36" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P36" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web).</t>
+          <t>Reprogramada desde el Sprint 2 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el unico actor es el tecnico. La consulta de la serie vive en HU-045 (web). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3547,10 +3663,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O37" s="12" t="n"/>
+      <c r="O37" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P37" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3618,10 +3738,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O38" s="12" t="n"/>
+      <c r="O38" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P38" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 2 (Sprint Review 1). La parte web sigue en el Sprint 2; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3820,7 @@
       </c>
       <c r="P39" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia.</t>
+          <t>Reprogramada desde el Sprint 3 (Sprint Review 1, 15-09-2026). Lado servidor listo el 16-09-2026: compuerta 402 (SuscripcionHandler) y descarga por sabana. Lo movil (T-3009/T-3011) es el MVP de la app que trabaja Bryan y no se marca todavia. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3764,10 +3888,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O40" s="12" t="n"/>
+      <c r="O40" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P40" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3835,10 +3963,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O41" s="12" t="n"/>
+      <c r="O41" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P41" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3906,10 +4038,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O42" s="12" t="n"/>
+      <c r="O42" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P42" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -3977,10 +4113,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O43" s="12" t="n"/>
+      <c r="O43" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P43" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4048,10 +4188,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O44" s="12" t="n"/>
+      <c r="O44" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P44" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4119,10 +4263,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O45" s="12" t="n"/>
+      <c r="O45" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P45" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4190,10 +4338,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O46" s="12" t="n"/>
+      <c r="O46" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P46" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 3 (Sprint Review 1). La parte web sigue en el Sprint 3; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4263,12 +4415,12 @@
       </c>
       <c r="O47" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="P47" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Hecho y verificado el 12-09-2026; pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Hecho y verificado el 12-09-2026; pendiente validación de la PO. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4495,7 @@
       </c>
       <c r="P48" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Catalina. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4418,7 +4570,7 @@
       </c>
       <c r="P49" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4645,7 @@
       </c>
       <c r="P50" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4563,12 +4715,12 @@
       </c>
       <c r="O51" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="P51" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio.</t>
+          <t>Reprogramada desde el Sprint 4 (Sprint Review 1, 15-09-2026). Tareas de Bryan (pruebas/doc) terminadas: probar_hu_bryan.py por HTTP. Estado lo cierra Emilio. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4636,10 +4788,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O52" s="12" t="n"/>
+      <c r="O52" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P52" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 4 (Sprint Review 1). La parte web sigue en el Sprint 4; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 4 (Sprint Review 1). La parte web sigue en el Sprint 4; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4707,10 +4863,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O53" s="12" t="n"/>
+      <c r="O53" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P53" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4945,7 @@
       </c>
       <c r="P54" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy la regla de obligatorios pasó al SP (BD/227). Pendiente validación de la PO. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4853,10 +5013,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O55" s="12" t="n"/>
+      <c r="O55" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P55" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4931,7 +5095,7 @@
       </c>
       <c r="P56" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; verificada por HTTP hoy. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -4999,10 +5163,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O57" s="12" t="n"/>
+      <c r="O57" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P57" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5077,7 +5245,7 @@
       </c>
       <c r="P58" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida en la app; verificada por HTTP hoy (probar_ot_app.py). Pendiente validación de la PO. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5320,7 @@
       </c>
       <c r="P59" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy se destrabó el consumo del técnico (ubicaciones de bodega). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5227,7 +5395,7 @@
       </c>
       <c r="P60" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). BD/227: obligatorios pendientes rechazados con nombres, resultado y fecha fin real, advertencia sin mano de obra. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5470,7 @@
       </c>
       <c r="P61" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). A nombre de Bryan (14-09-2026). Ya estaba construida; hoy el ejecutante inválido se rechaza con mensaje (BD/227). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5370,10 +5538,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O62" s="12" t="n"/>
+      <c r="O62" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P62" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5441,10 +5613,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O63" s="12" t="n"/>
+      <c r="O63" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P63" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5512,10 +5688,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O64" s="12" t="n"/>
+      <c r="O64" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P64" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131.</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · ALCANCE APP (30-08): App y Web → App. Solo App (R3): el tecnico escribe. Comentar y rectificar es HU-131. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5583,10 +5763,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O65" s="12" t="n"/>
+      <c r="O65" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P65" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5654,10 +5838,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O66" s="12" t="n"/>
+      <c r="O66" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P66" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5725,10 +5913,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O67" s="12" t="n"/>
+      <c r="O67" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P67" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5796,10 +5988,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O68" s="12" t="n"/>
+      <c r="O68" s="12" t="inlineStr">
+        <is>
+          <t>Catalina Pescio</t>
+        </is>
+      </c>
       <c r="P68" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5867,10 +6063,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O69" s="12" t="n"/>
+      <c r="O69" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P69" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -5938,10 +6138,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O70" s="12" t="n"/>
+      <c r="O70" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P70" s="12" t="inlineStr">
         <is>
-          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026).</t>
+          <t>Reprogramada desde el Sprint 5 (Sprint Review 1, 15-09-2026). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -6009,10 +6213,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O71" s="12" t="n"/>
+      <c r="O71" s="12" t="inlineStr">
+        <is>
+          <t>Emilio Fuentes</t>
+        </is>
+      </c>
       <c r="P71" s="12" t="inlineStr">
         <is>
-          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá.</t>
+          <t>Solo las tareas Móvil, reprogramadas desde el Sprint 5 (Sprint Review 1). La parte web sigue en el Sprint 5; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -6080,10 +6288,14 @@
           <t>Por hacer</t>
         </is>
       </c>
-      <c r="O72" s="12" t="n"/>
+      <c r="O72" s="12" t="inlineStr">
+        <is>
+          <t>Bryan Chávez</t>
+        </is>
+      </c>
       <c r="P72" s="12" t="inlineStr">
         <is>
-          <t>Solo la tarea de infraestructura (clave de Google Maps). La historia sigue en el Sprint 1.</t>
+          <t>Solo la tarea de infraestructura (clave de Google Maps). La historia sigue en el Sprint 1. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -6153,12 +6365,12 @@
       </c>
       <c r="O73" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="P73" s="12" t="inlineStr">
         <is>
-          <t>Solo la parte móvil, separada el 22-09-2026 (la historia era «Web y App» y no tenía ninguna tarea Móvil). La parte web se cerró en el Sprint 3 con 4/4 criterios; los puntos quedan allá.</t>
+          <t>Solo la parte móvil, separada el 22-09-2026 (la historia era «Web y App» y no tenía ninguna tarea Móvil). La parte web se cerró en el Sprint 3 con 4/4 criterios; los puntos quedan allá. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -6324,7 +6536,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H6" s="11" t="inlineStr">
@@ -6416,7 +6628,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H8" s="11" t="inlineStr">
@@ -6462,7 +6674,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H9" s="11" t="inlineStr">
@@ -6508,7 +6720,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H10" s="11" t="inlineStr">
@@ -6592,7 +6804,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H12" s="11" t="inlineStr">
@@ -6638,7 +6850,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H13" s="11" t="inlineStr">
@@ -6680,7 +6892,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H14" s="11" t="inlineStr">
@@ -6726,7 +6938,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H15" s="11" t="inlineStr">
@@ -6768,7 +6980,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H16" s="11" t="inlineStr">
@@ -6810,7 +7022,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H17" s="11" t="inlineStr">
@@ -6898,7 +7110,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H19" s="11" t="inlineStr">
@@ -6944,7 +7156,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H20" s="11" t="inlineStr">
@@ -7036,7 +7248,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H22" s="11" t="inlineStr">
@@ -7174,7 +7386,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H25" s="11" t="inlineStr">
@@ -7216,7 +7428,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H26" s="11" t="inlineStr">
@@ -7258,7 +7470,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H27" s="11" t="inlineStr">
@@ -7350,7 +7562,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H29" s="11" t="inlineStr">
@@ -7396,7 +7608,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H30" s="11" t="inlineStr">
@@ -7442,7 +7654,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H31" s="11" t="inlineStr">
@@ -7526,7 +7738,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H33" s="11" t="inlineStr">
@@ -7614,7 +7826,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H35" s="11" t="inlineStr">
@@ -7660,7 +7872,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H36" s="11" t="inlineStr">
@@ -7702,7 +7914,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H37" s="11" t="inlineStr">
@@ -8176,7 +8388,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H47" s="11" t="inlineStr">
@@ -8218,7 +8430,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H48" s="11" t="inlineStr">
@@ -8302,7 +8514,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H50" s="11" t="inlineStr">
@@ -8344,7 +8556,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H51" s="11" t="inlineStr">
@@ -8386,7 +8598,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H52" s="11" t="inlineStr">
@@ -8470,7 +8682,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H54" s="11" t="inlineStr">
@@ -8512,7 +8724,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H55" s="11" t="inlineStr">
@@ -8554,7 +8766,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H56" s="11" t="inlineStr">
@@ -8596,7 +8808,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H57" s="11" t="inlineStr">
@@ -8638,7 +8850,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H58" s="11" t="inlineStr">
@@ -8680,7 +8892,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H59" s="11" t="inlineStr">
@@ -9202,7 +9414,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H70" s="11" t="inlineStr">
@@ -9248,7 +9460,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H71" s="11" t="inlineStr">
@@ -9340,7 +9552,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H73" s="11" t="inlineStr">
@@ -9386,7 +9598,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H74" s="11" t="inlineStr">
@@ -9432,7 +9644,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H75" s="11" t="inlineStr">
@@ -10952,7 +11164,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H107" s="11" t="inlineStr">
@@ -10998,7 +11210,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H108" s="11" t="inlineStr">
@@ -11090,7 +11302,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H110" s="11" t="inlineStr">
@@ -11132,7 +11344,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H111" s="11" t="inlineStr">
@@ -11174,7 +11386,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H112" s="11" t="inlineStr">
@@ -11220,7 +11432,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H113" s="11" t="inlineStr">
@@ -11262,7 +11474,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H114" s="11" t="inlineStr">
@@ -11392,7 +11604,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H117" s="11" t="inlineStr">
@@ -11438,7 +11650,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H118" s="11" t="inlineStr">
@@ -11530,7 +11742,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H120" s="11" t="inlineStr">
@@ -11576,7 +11788,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H121" s="11" t="inlineStr">
@@ -11622,7 +11834,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H122" s="11" t="inlineStr">
@@ -11668,7 +11880,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H123" s="11" t="inlineStr">
@@ -11886,7 +12098,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H128" s="11" t="inlineStr">
@@ -11932,7 +12144,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H129" s="11" t="inlineStr">
@@ -12024,7 +12236,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H131" s="11" t="inlineStr">
@@ -12070,7 +12282,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H132" s="11" t="inlineStr">
@@ -12116,7 +12328,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H133" s="11" t="inlineStr">
@@ -12330,7 +12542,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H138" s="11" t="inlineStr">
@@ -12372,7 +12584,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H139" s="11" t="inlineStr">
@@ -12462,7 +12674,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H141" s="11" t="inlineStr">
@@ -12504,7 +12716,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H142" s="11" t="inlineStr">
@@ -12546,7 +12758,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H143" s="11" t="inlineStr">
@@ -12630,7 +12842,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H145" s="11" t="inlineStr">
@@ -12720,7 +12932,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H147" s="11" t="inlineStr">
@@ -12762,7 +12974,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H148" s="11" t="inlineStr">
@@ -12804,7 +13016,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H149" s="11" t="inlineStr">
@@ -12892,7 +13104,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H151" s="11" t="inlineStr">
@@ -12938,7 +13150,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H152" s="11" t="inlineStr">
@@ -13032,7 +13244,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H154" s="11" t="inlineStr">
@@ -13124,7 +13336,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H156" s="11" t="inlineStr">
@@ -13172,7 +13384,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H157" s="11" t="inlineStr">
@@ -13214,7 +13426,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H158" s="11" t="inlineStr">
@@ -13256,7 +13468,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H159" s="11" t="inlineStr">
@@ -13298,7 +13510,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H160" s="11" t="inlineStr">
@@ -13344,7 +13556,7 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H161" s="11" t="inlineStr">
@@ -13386,7 +13598,7 @@
       </c>
       <c r="G162" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H162" s="11" t="inlineStr">
@@ -13428,7 +13640,7 @@
       </c>
       <c r="G163" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H163" s="11" t="inlineStr">
@@ -13474,7 +13686,7 @@
       </c>
       <c r="G164" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H164" s="11" t="inlineStr">
@@ -13516,7 +13728,7 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H165" s="11" t="inlineStr">
@@ -13610,7 +13822,7 @@
       </c>
       <c r="G167" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H167" s="11" t="inlineStr">
@@ -13656,7 +13868,7 @@
       </c>
       <c r="G168" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H168" s="11" t="inlineStr">
@@ -13750,7 +13962,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H170" s="11" t="inlineStr">
@@ -13840,7 +14052,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H172" s="11" t="inlineStr">
@@ -13882,7 +14094,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H173" s="11" t="inlineStr">
@@ -13924,7 +14136,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H174" s="11" t="inlineStr">
@@ -14012,7 +14224,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H176" s="11" t="inlineStr">
@@ -14058,7 +14270,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H177" s="11" t="inlineStr">
@@ -14150,7 +14362,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H179" s="11" t="inlineStr">
@@ -14196,7 +14408,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H180" s="11" t="inlineStr">
@@ -14242,7 +14454,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H181" s="11" t="inlineStr">
@@ -14372,7 +14584,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H184" s="11" t="inlineStr">
@@ -14464,7 +14676,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H186" s="11" t="inlineStr">
@@ -14510,7 +14722,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H187" s="11" t="inlineStr">
@@ -14556,7 +14768,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H188" s="11" t="inlineStr">
@@ -14602,7 +14814,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H189" s="11" t="inlineStr">
@@ -14774,7 +14986,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H193" s="11" t="inlineStr">
@@ -14820,7 +15032,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H194" s="11" t="inlineStr">
@@ -14912,7 +15124,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H196" s="11" t="inlineStr">
@@ -15004,7 +15216,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H198" s="11" t="inlineStr">
@@ -15050,7 +15262,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H199" s="11" t="inlineStr">
@@ -15092,7 +15304,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H200" s="11" t="inlineStr">
@@ -15134,7 +15346,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H201" s="11" t="inlineStr">
@@ -15606,7 +15818,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H211" s="11" t="inlineStr">
@@ -15744,7 +15956,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H214" s="11" t="inlineStr">
@@ -15928,7 +16140,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H218" s="11" t="inlineStr">
@@ -16250,7 +16462,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H225" s="11" t="inlineStr">
@@ -16388,7 +16600,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H228" s="11" t="inlineStr">
@@ -16434,7 +16646,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H229" s="11" t="inlineStr">
@@ -16480,7 +16692,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H230" s="11" t="inlineStr">
@@ -16526,7 +16738,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H231" s="11" t="inlineStr">
@@ -16572,7 +16784,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H232" s="11" t="inlineStr">
@@ -16664,7 +16876,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H234" s="11" t="inlineStr">
@@ -16710,7 +16922,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H235" s="11" t="inlineStr">
@@ -16802,7 +17014,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H237" s="11" t="inlineStr">
@@ -16894,7 +17106,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H239" s="11" t="inlineStr">
@@ -17032,7 +17244,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H242" s="11" t="inlineStr">
@@ -17078,7 +17290,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H243" s="11" t="inlineStr">
@@ -17170,7 +17382,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H245" s="11" t="inlineStr">
@@ -17216,7 +17428,7 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H246" s="11" t="inlineStr">
@@ -17308,7 +17520,7 @@
       </c>
       <c r="G248" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H248" s="11" t="inlineStr">
@@ -17400,7 +17612,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H250" s="11" t="inlineStr">
@@ -17492,7 +17704,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H252" s="11" t="inlineStr">
@@ -17630,7 +17842,7 @@
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H255" s="11" t="inlineStr">
@@ -17676,7 +17888,7 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H256" s="11" t="inlineStr">
@@ -17722,7 +17934,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H257" s="11" t="inlineStr">
@@ -17814,7 +18026,7 @@
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H259" s="11" t="inlineStr">
@@ -17860,7 +18072,7 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H260" s="11" t="inlineStr">
@@ -17952,7 +18164,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H262" s="11" t="inlineStr">
@@ -18044,7 +18256,7 @@
       </c>
       <c r="G264" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H264" s="11" t="inlineStr">
@@ -18182,7 +18394,7 @@
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H267" s="11" t="inlineStr">
@@ -18228,7 +18440,7 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H268" s="11" t="inlineStr">
@@ -18274,7 +18486,7 @@
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H269" s="11" t="inlineStr">
@@ -18412,7 +18624,7 @@
       </c>
       <c r="G272" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H272" s="11" t="inlineStr">
@@ -18458,7 +18670,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H273" s="11" t="inlineStr">
@@ -18596,7 +18808,7 @@
       </c>
       <c r="G276" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H276" s="11" t="inlineStr">
@@ -18734,7 +18946,7 @@
       </c>
       <c r="G279" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H279" s="11" t="inlineStr">
@@ -18872,7 +19084,7 @@
       </c>
       <c r="G282" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H282" s="11" t="inlineStr">
@@ -18918,7 +19130,7 @@
       </c>
       <c r="G283" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H283" s="11" t="inlineStr">
@@ -18964,7 +19176,7 @@
       </c>
       <c r="G284" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H284" s="11" t="inlineStr">
@@ -19056,7 +19268,7 @@
       </c>
       <c r="G286" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H286" s="11" t="inlineStr">
@@ -19148,7 +19360,7 @@
       </c>
       <c r="G288" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H288" s="11" t="inlineStr">
@@ -19240,7 +19452,7 @@
       </c>
       <c r="G290" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H290" s="11" t="inlineStr">
@@ -19332,7 +19544,7 @@
       </c>
       <c r="G292" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H292" s="11" t="inlineStr">
@@ -19378,7 +19590,7 @@
       </c>
       <c r="G293" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H293" s="11" t="inlineStr">
@@ -19424,7 +19636,7 @@
       </c>
       <c r="G294" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H294" s="11" t="inlineStr">
@@ -19470,7 +19682,7 @@
       </c>
       <c r="G295" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H295" s="11" t="inlineStr">
@@ -19516,7 +19728,7 @@
       </c>
       <c r="G296" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H296" s="11" t="inlineStr">
@@ -19562,7 +19774,7 @@
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H297" s="11" t="inlineStr">
@@ -19608,7 +19820,7 @@
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H298" s="11" t="inlineStr">
@@ -19654,7 +19866,7 @@
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H299" s="11" t="inlineStr">
@@ -19700,7 +19912,7 @@
       </c>
       <c r="G300" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H300" s="11" t="inlineStr">
@@ -19746,7 +19958,7 @@
       </c>
       <c r="G301" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H301" s="11" t="inlineStr">
@@ -19792,7 +20004,7 @@
       </c>
       <c r="G302" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H302" s="11" t="inlineStr">
@@ -19838,7 +20050,7 @@
       </c>
       <c r="G303" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H303" s="11" t="inlineStr">
@@ -19884,7 +20096,7 @@
       </c>
       <c r="G304" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H304" s="11" t="inlineStr">
@@ -19930,7 +20142,7 @@
       </c>
       <c r="G305" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H305" s="11" t="inlineStr">
@@ -20482,7 +20694,7 @@
       </c>
       <c r="G317" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H317" s="11" t="inlineStr">
@@ -20528,7 +20740,7 @@
       </c>
       <c r="G318" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H318" s="11" t="inlineStr">
@@ -21080,7 +21292,7 @@
       </c>
       <c r="G330" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H330" s="11" t="inlineStr">
@@ -21126,7 +21338,7 @@
       </c>
       <c r="G331" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H331" s="11" t="inlineStr">
@@ -21172,7 +21384,7 @@
       </c>
       <c r="G332" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H332" s="11" t="inlineStr">
@@ -21724,7 +21936,7 @@
       </c>
       <c r="G344" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H344" s="11" t="inlineStr">
@@ -21770,7 +21982,7 @@
       </c>
       <c r="G345" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H345" s="11" t="inlineStr">
@@ -21816,7 +22028,7 @@
       </c>
       <c r="G346" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H346" s="11" t="inlineStr">
@@ -21862,7 +22074,7 @@
       </c>
       <c r="G347" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H347" s="11" t="inlineStr">
@@ -21908,7 +22120,7 @@
       </c>
       <c r="G348" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H348" s="11" t="inlineStr">
@@ -21954,7 +22166,7 @@
       </c>
       <c r="G349" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H349" s="11" t="inlineStr">
@@ -22000,7 +22212,7 @@
       </c>
       <c r="G350" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H350" s="11" t="inlineStr">
@@ -22046,7 +22258,7 @@
       </c>
       <c r="G351" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H351" s="11" t="inlineStr">
@@ -22092,7 +22304,7 @@
       </c>
       <c r="G352" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H352" s="11" t="inlineStr">
@@ -22138,7 +22350,7 @@
       </c>
       <c r="G353" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H353" s="11" t="inlineStr">
@@ -22184,7 +22396,7 @@
       </c>
       <c r="G354" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H354" s="11" t="inlineStr">
@@ -22230,7 +22442,7 @@
       </c>
       <c r="G355" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H355" s="11" t="inlineStr">
@@ -22276,7 +22488,7 @@
       </c>
       <c r="G356" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H356" s="11" t="inlineStr">
@@ -22322,7 +22534,7 @@
       </c>
       <c r="G357" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H357" s="11" t="inlineStr">
@@ -22368,7 +22580,7 @@
       </c>
       <c r="G358" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H358" s="11" t="inlineStr">
@@ -22414,7 +22626,7 @@
       </c>
       <c r="G359" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H359" s="11" t="inlineStr">
@@ -22460,7 +22672,7 @@
       </c>
       <c r="G360" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H360" s="11" t="inlineStr">
@@ -23242,7 +23454,7 @@
       </c>
       <c r="G377" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H377" s="11" t="inlineStr">
@@ -23288,7 +23500,7 @@
       </c>
       <c r="G378" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H378" s="11" t="inlineStr">
@@ -23426,7 +23638,7 @@
       </c>
       <c r="G381" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H381" s="11" t="inlineStr">
@@ -23564,7 +23776,7 @@
       </c>
       <c r="G384" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H384" s="11" t="inlineStr">
@@ -23702,7 +23914,7 @@
       </c>
       <c r="G387" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H387" s="11" t="inlineStr">
@@ -23748,7 +23960,7 @@
       </c>
       <c r="G388" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H388" s="11" t="inlineStr">
@@ -23794,7 +24006,7 @@
       </c>
       <c r="G389" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H389" s="11" t="inlineStr">
@@ -26554,7 +26766,7 @@
       </c>
       <c r="G449" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H449" s="11" t="inlineStr">
@@ -26646,7 +26858,7 @@
       </c>
       <c r="G451" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H451" s="11" t="inlineStr">
@@ -26692,7 +26904,7 @@
       </c>
       <c r="G452" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H452" s="11" t="inlineStr">
@@ -26830,7 +27042,7 @@
       </c>
       <c r="G455" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H455" s="11" t="inlineStr">
@@ -26968,7 +27180,7 @@
       </c>
       <c r="G458" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H458" s="11" t="inlineStr">
@@ -27014,7 +27226,7 @@
       </c>
       <c r="G459" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H459" s="11" t="inlineStr">
@@ -27060,7 +27272,7 @@
       </c>
       <c r="G460" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H460" s="11" t="inlineStr">
@@ -27106,7 +27318,7 @@
       </c>
       <c r="G461" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H461" s="11" t="inlineStr">
@@ -27198,7 +27410,7 @@
       </c>
       <c r="G463" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H463" s="11" t="inlineStr">
@@ -27244,7 +27456,7 @@
       </c>
       <c r="G464" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H464" s="11" t="inlineStr">
@@ -27336,7 +27548,7 @@
       </c>
       <c r="G466" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H466" s="11" t="inlineStr">
@@ -27382,7 +27594,7 @@
       </c>
       <c r="G467" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H467" s="11" t="inlineStr">
@@ -27428,7 +27640,7 @@
       </c>
       <c r="G468" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H468" s="11" t="inlineStr">
@@ -27474,7 +27686,7 @@
       </c>
       <c r="G469" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H469" s="11" t="inlineStr">
@@ -27658,7 +27870,7 @@
       </c>
       <c r="G473" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H473" s="11" t="inlineStr">
@@ -27704,7 +27916,7 @@
       </c>
       <c r="G474" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H474" s="11" t="inlineStr">
@@ -27796,7 +28008,7 @@
       </c>
       <c r="G476" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H476" s="11" t="inlineStr">
@@ -27842,7 +28054,7 @@
       </c>
       <c r="G477" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H477" s="11" t="inlineStr">
@@ -27888,7 +28100,7 @@
       </c>
       <c r="G478" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H478" s="11" t="inlineStr">
@@ -27934,7 +28146,7 @@
       </c>
       <c r="G479" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H479" s="11" t="inlineStr">
@@ -27980,7 +28192,7 @@
       </c>
       <c r="G480" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H480" s="11" t="inlineStr">
@@ -28026,7 +28238,7 @@
       </c>
       <c r="G481" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H481" s="11" t="inlineStr">
@@ -28072,7 +28284,7 @@
       </c>
       <c r="G482" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H482" s="11" t="inlineStr">
@@ -28118,7 +28330,7 @@
       </c>
       <c r="G483" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H483" s="11" t="inlineStr">
@@ -28348,7 +28560,7 @@
       </c>
       <c r="G488" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H488" s="11" t="inlineStr">
@@ -28394,7 +28606,7 @@
       </c>
       <c r="G489" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H489" s="11" t="inlineStr">
@@ -28440,7 +28652,7 @@
       </c>
       <c r="G490" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H490" s="11" t="inlineStr">
@@ -28532,7 +28744,7 @@
       </c>
       <c r="G492" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H492" s="11" t="inlineStr">
@@ -28578,7 +28790,7 @@
       </c>
       <c r="G493" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H493" s="11" t="inlineStr">
@@ -28670,7 +28882,7 @@
       </c>
       <c r="G495" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H495" s="11" t="inlineStr">
@@ -28716,7 +28928,7 @@
       </c>
       <c r="G496" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H496" s="11" t="inlineStr">
@@ -28762,7 +28974,7 @@
       </c>
       <c r="G497" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H497" s="11" t="inlineStr">
@@ -28808,7 +29020,7 @@
       </c>
       <c r="G498" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H498" s="11" t="inlineStr">
@@ -28854,7 +29066,7 @@
       </c>
       <c r="G499" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H499" s="11" t="inlineStr">
@@ -28900,7 +29112,7 @@
       </c>
       <c r="G500" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H500" s="11" t="inlineStr">
@@ -28992,7 +29204,7 @@
       </c>
       <c r="G502" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H502" s="11" t="inlineStr">
@@ -29084,7 +29296,7 @@
       </c>
       <c r="G504" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H504" s="11" t="inlineStr">
@@ -29176,7 +29388,7 @@
       </c>
       <c r="G506" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H506" s="11" t="inlineStr">
@@ -29268,7 +29480,7 @@
       </c>
       <c r="G508" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H508" s="11" t="inlineStr">
@@ -29314,7 +29526,7 @@
       </c>
       <c r="G509" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H509" s="11" t="inlineStr">
@@ -29360,7 +29572,7 @@
       </c>
       <c r="G510" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H510" s="11" t="inlineStr">
@@ -29406,7 +29618,7 @@
       </c>
       <c r="G511" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H511" s="11" t="inlineStr">
@@ -29544,7 +29756,7 @@
       </c>
       <c r="G514" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H514" s="11" t="inlineStr">
@@ -29590,7 +29802,7 @@
       </c>
       <c r="G515" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H515" s="11" t="inlineStr">
@@ -29774,7 +29986,7 @@
       </c>
       <c r="G519" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H519" s="11" t="inlineStr">

--- a/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
+++ b/Fase 2/Evidencias Proyecto/Sprint Backlogs/SIGMA_Sprint_Backlog_S6.xlsx
@@ -1335,7 +1335,7 @@
       </c>
       <c r="N6" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O6" s="12" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="P6" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Inicio con el widget SIGMA AI (predicciones vigentes con anillo, razones y curva) y el Centro de monitoreo 3D (View/SigmaAI/Centro.aspx, WsAiCentro, BD/379). Falta el panel compacto de la app (CA5). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O7" s="14" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="P7" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Crear OT en 2 clics desde la predicción (WsAlertas.GenerarOrden) con origen predicción y razones precargadas. La fecha programada propuesta (CA2) se dejó fuera a propósito: BD/117 decide que programar es una decisión de planificación con dotación y repuestos a la vista. El descarte pide motivo de una lista más detalle opcional, no 10 caracteres (CA4). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="N8" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O8" s="12" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="P8" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El detalle de la predicción muestra razones ordenadas por peso (SEL_AI_DETALLE) y el Copiloto las explica con reglas. Falta el intervalo de la estimación con su confianza (CA3) y la serie de la variable determinante con banda normal (CA2). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O9" s="14" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="P9" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Mantenimiento › Indicadores › Tablero (BD/474, WsIndicadores): cumplimiento, disponibilidad, tiempo medio entre fallas, tiempo medio de reparación y órdenes pendientes de cierre con su variación contra el período anterior (CA1); filtros de planta, área, equipo y fechas que recalculan todo (CA2); cada indicador abre su detalle en un cajón (CA3).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1710,17 +1710,17 @@
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="P11" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Pantalla SIGMA AI › Desempeño › «Por evaluar» (View/SigmaAI/Desempeno.aspx, WsAiDesempeno, BD/475): lista las predicciones con el horizonte vencido sin evaluar (CA3), registra si el evento ocurrió y cuándo con el error en días calculado por el SP (CA1) y clasifica «acierto con intervención» aparte de la falsa alarma (CA2).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="N12" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O12" s="12" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="P12" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El tablero y Operación › Cumplimiento miden hechas sobre vencidas contra la fecha original (CA1) y ordenan los equipos del peor al mejor (CA3). El desglose completo (CA2) distingue hechas y vencidas; faltan reprogramadas y omitidas por separado. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O13" s="14" t="inlineStr">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P13" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Tablero e indicadores (BD/474): disponibilidad con la indisponibilidad no planificada descontada y la planificada aparte (CA1); tiempo medio entre fallas con aviso cuando hay menos de 3 fallas (CA2); tiempo medio de reparación sobre las correctivas cerradas (CA3).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="N14" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O14" s="12" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="P14" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Mantenimiento › Indicadores › Costos (BD/474): repuestos, mano de obra y servicios por equipo y siempre por moneda (CA1); por centro de costo con el de sus dependientes (CA2, probado con un árbol de prueba revertido); comparación con el período anterior en variación absoluta y porcentual (CA3).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2010,17 +2010,17 @@
       </c>
       <c r="N15" s="13" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Centro de carga de datos (BD/334, 335, 368, 473, 476): revisión sin escribir (CA1), aviso de que la planilla ya se procesó, con fecha y usuario, gracias a la huella SHA-256 del archivo (CA2), carga confirmada (CA3) y plantilla con ejemplo (CA4).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="N16" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O16" s="12" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="P16" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: La campana y «Requieren tu atención» unen alertas por severidad y antigüedad, y la alerta no crea trabajo sola (CA1 y CA3); se atiende o descarta con motivo. Falta la hoja propia de la bandeja con filtros y exportación. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Cada celda con error se informa con hoja, fila, columna, valor y motivo, y una fila mala no detiene la carga (CA1 y CA4). Falta corregir la celda dentro de la pantalla y aplicar la corrección a todas las coincidencias (CA2 y CA3): hoy se corrige en la planilla y se revisa de nuevo. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2235,7 +2235,7 @@
       </c>
       <c r="N18" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O18" s="12" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="P18" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El módulo Mantenimiento carga frecuencias, tareas, checklists, planes, hitos, actividades y equipos (BD/473) y el plan queda en borrador salvo ACTIVAR = SI (CA1 y CA3). Falta que una frecuencia ambigua pida elegir la interpretación (CA2): hoy se rechaza con el motivo. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="N22" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O22" s="12" t="inlineStr">
@@ -2545,7 +2545,7 @@
       </c>
       <c r="P22" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Excel con los mismos filtros de la pantalla y encabezado de cliente, período y filtros (CA1) e impresión con el pie del cliente (CA2), para el tablero, el detalle de cada indicador y los costos. Falta ofrecerlos en los demás listados de SIGMA (Operación, órdenes, activos). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O23" s="14" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Centro de SIGMA AI › Fotos de terreno: cada detección se presenta «por confirmar» y no como confirmada hasta que una persona la confirma o corrige (CA3 y CA4), y esa decisión alimenta el dataset. Falta la cola de análisis con prioridad (CA1) y dibujar las zonas detectadas sobre la imagen (CA2). · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="N24" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O24" s="12" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="P24" s="12" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: Pestaña «Desempeño» (BD/475): por versión y mes, predicciones, evaluadas, aciertos, falsas alarmas y aciertos con intervención aparte (CA1); la versión queda «candidata a reentrenamiento» si la precisión cae bajo la de referencia con al menos 5 evaluadas (CA2). Falta la desviación de los datos de entrada (CA3): no se guarda la distribución del entrenamiento. · Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -2760,17 +2760,17 @@
       </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Terminada</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>Avance web al 17-10-2026: El historial guarda cada revisión y carga con archivo, fecha, usuario, módulo y resultado (CA1); al abrir una carga se ve el resultado por hoja, con filas, creadas, actualizadas, omitidas y errores (CA2).</t>
+          <t>Dueño único desde el 17-10-2026: hace desarrollo, pruebas, documentación y validación.</t>
         </is>
       </c>
     </row>
@@ -6541,15 +6541,11 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
     </row>
     <row r="7" ht="41.4" customHeight="1" s="19">
       <c r="A7" s="11" t="inlineStr">
@@ -6587,15 +6583,11 @@
       </c>
       <c r="H7" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I7" s="11" t="n"/>
-      <c r="J7" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J7" s="12" t="n"/>
     </row>
     <row r="8" ht="27.6" customHeight="1" s="19">
       <c r="A8" s="11" t="inlineStr">
@@ -6633,15 +6625,11 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I8" s="11" t="n"/>
-      <c r="J8" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J8" s="12" t="n"/>
     </row>
     <row r="9" ht="27.6" customHeight="1" s="19">
       <c r="A9" s="11" t="inlineStr">
@@ -6679,15 +6667,11 @@
       </c>
       <c r="H9" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I9" s="11" t="n"/>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J9" s="12" t="n"/>
     </row>
     <row r="10" ht="27.6" customHeight="1" s="19">
       <c r="A10" s="11" t="inlineStr">
@@ -6809,15 +6793,11 @@
       </c>
       <c r="H12" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I12" s="11" t="n"/>
-      <c r="J12" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J12" s="12" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -6897,15 +6877,11 @@
       </c>
       <c r="H14" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I14" s="11" t="n"/>
-      <c r="J14" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J14" s="12" t="n"/>
     </row>
     <row r="15" ht="41.4" customHeight="1" s="19">
       <c r="A15" s="11" t="inlineStr">
@@ -7069,15 +7045,11 @@
       </c>
       <c r="H18" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I18" s="11" t="n"/>
-      <c r="J18" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J18" s="12" t="n"/>
     </row>
     <row r="19" ht="41.4" customHeight="1" s="19">
       <c r="A19" s="11" t="inlineStr">
@@ -7115,15 +7087,11 @@
       </c>
       <c r="H19" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I19" s="11" t="n"/>
-      <c r="J19" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J19" s="12" t="n"/>
     </row>
     <row r="20" ht="27.6" customHeight="1" s="19">
       <c r="A20" s="11" t="inlineStr">
@@ -7161,15 +7129,11 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I20" s="11" t="n"/>
-      <c r="J20" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J20" s="12" t="n"/>
     </row>
     <row r="21" ht="27.6" customHeight="1" s="19">
       <c r="A21" s="11" t="inlineStr">
@@ -7207,15 +7171,11 @@
       </c>
       <c r="H21" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J21" s="12" t="n"/>
     </row>
     <row r="22" ht="27.6" customHeight="1" s="19">
       <c r="A22" s="11" t="inlineStr">
@@ -7253,15 +7213,11 @@
       </c>
       <c r="H22" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I22" s="11" t="n"/>
-      <c r="J22" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J22" s="12" t="n"/>
     </row>
     <row r="23" ht="27.6" customHeight="1" s="19">
       <c r="A23" s="11" t="inlineStr">
@@ -7299,15 +7255,11 @@
       </c>
       <c r="H23" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I23" s="11" t="n"/>
-      <c r="J23" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J23" s="12" t="n"/>
     </row>
     <row r="24" ht="27.6" customHeight="1" s="19">
       <c r="A24" s="11" t="inlineStr">
@@ -7345,15 +7297,11 @@
       </c>
       <c r="H24" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I24" s="11" t="n"/>
-      <c r="J24" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J24" s="12" t="n"/>
     </row>
     <row r="25" ht="41.4" customHeight="1" s="19">
       <c r="A25" s="11" t="inlineStr">
@@ -7475,15 +7423,11 @@
       </c>
       <c r="H27" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I27" s="11" t="n"/>
-      <c r="J27" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J27" s="12" t="n"/>
     </row>
     <row r="28" ht="41.4" customHeight="1" s="19">
       <c r="A28" s="11" t="inlineStr">
@@ -7521,15 +7465,11 @@
       </c>
       <c r="H28" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I28" s="11" t="n"/>
-      <c r="J28" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J28" s="12" t="n"/>
     </row>
     <row r="29" ht="27.6" customHeight="1" s="19">
       <c r="A29" s="11" t="inlineStr">
@@ -7567,15 +7507,11 @@
       </c>
       <c r="H29" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I29" s="11" t="n"/>
-      <c r="J29" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J29" s="12" t="n"/>
     </row>
     <row r="30" ht="41.4" customHeight="1" s="19">
       <c r="A30" s="11" t="inlineStr">
@@ -7613,15 +7549,11 @@
       </c>
       <c r="H30" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I30" s="11" t="n"/>
-      <c r="J30" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J30" s="12" t="n"/>
     </row>
     <row r="31" ht="27.6" customHeight="1" s="19">
       <c r="A31" s="11" t="inlineStr">
@@ -7743,15 +7675,11 @@
       </c>
       <c r="H33" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I33" s="11" t="n"/>
-      <c r="J33" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J33" s="12" t="n"/>
     </row>
     <row r="34" ht="27.6" customHeight="1" s="19">
       <c r="A34" s="11" t="inlineStr">
@@ -7831,15 +7759,11 @@
       </c>
       <c r="H35" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I35" s="11" t="n"/>
-      <c r="J35" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J35" s="12" t="n"/>
     </row>
     <row r="36" ht="41.4" customHeight="1" s="19">
       <c r="A36" s="11" t="inlineStr">
@@ -7956,22 +7880,16 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H38" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I38" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J38" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="12" t="n"/>
     </row>
     <row r="39" ht="41.4" customHeight="1" s="19">
       <c r="A39" s="11" t="inlineStr">
@@ -8004,22 +7922,16 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H39" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J39" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="12" t="n"/>
     </row>
     <row r="40" ht="41.4" customHeight="1" s="19">
       <c r="A40" s="11" t="inlineStr">
@@ -8057,17 +7969,11 @@
       </c>
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J40" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="12" t="n"/>
     </row>
     <row r="41" ht="41.4" customHeight="1" s="19">
       <c r="A41" s="11" t="inlineStr">
@@ -8100,22 +8006,16 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I41" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="12" t="n"/>
     </row>
     <row r="42" ht="27.6" customHeight="1" s="19">
       <c r="A42" s="11" t="inlineStr">
@@ -8148,22 +8048,16 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I42" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J42" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="12" t="n"/>
     </row>
     <row r="43" ht="27.6" customHeight="1" s="19">
       <c r="A43" s="11" t="inlineStr">
@@ -8196,22 +8090,16 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H43" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I43" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="12" t="n"/>
     </row>
     <row r="44" ht="27.6" customHeight="1" s="19">
       <c r="A44" s="11" t="inlineStr">
@@ -8244,22 +8132,16 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H44" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I44" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="12" t="n"/>
     </row>
     <row r="45" ht="27.6" customHeight="1" s="19">
       <c r="A45" s="11" t="inlineStr">
@@ -8292,22 +8174,16 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H45" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I45" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="12" t="n"/>
     </row>
     <row r="46" ht="27.6" customHeight="1" s="19">
       <c r="A46" s="11" t="inlineStr">
@@ -8340,22 +8216,16 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H46" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I46" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J46" s="12" t="inlineStr">
-        <is>
-          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="12" t="n"/>
     </row>
     <row r="47" ht="55.2" customHeight="1" s="19">
       <c r="A47" s="11" t="inlineStr">
@@ -8939,17 +8809,11 @@
       </c>
       <c r="H60" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I60" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J60" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="12" t="n"/>
     </row>
     <row r="61" ht="41.4" customHeight="1" s="19">
       <c r="A61" s="11" t="inlineStr">
@@ -8982,22 +8846,16 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H61" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I61" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J61" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="12" t="n"/>
     </row>
     <row r="62" ht="41.4" customHeight="1" s="19">
       <c r="A62" s="11" t="inlineStr">
@@ -9030,22 +8888,16 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H62" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I62" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J62" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I62" s="11" t="n"/>
+      <c r="J62" s="12" t="n"/>
     </row>
     <row r="63" ht="27.6" customHeight="1" s="19">
       <c r="A63" s="11" t="inlineStr">
@@ -9083,17 +8935,11 @@
       </c>
       <c r="H63" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I63" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J63" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I63" s="11" t="n"/>
+      <c r="J63" s="12" t="n"/>
     </row>
     <row r="64" ht="27.6" customHeight="1" s="19">
       <c r="A64" s="11" t="inlineStr">
@@ -9126,22 +8972,16 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H64" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I64" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J64" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I64" s="11" t="n"/>
+      <c r="J64" s="12" t="n"/>
     </row>
     <row r="65" ht="41.4" customHeight="1" s="19">
       <c r="A65" s="11" t="inlineStr">
@@ -9179,17 +9019,11 @@
       </c>
       <c r="H65" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I65" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J65" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="12" t="n"/>
     </row>
     <row r="66" ht="27.6" customHeight="1" s="19">
       <c r="A66" s="11" t="inlineStr">
@@ -9222,22 +9056,16 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H66" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I66" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J66" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="12" t="n"/>
     </row>
     <row r="67" ht="27.6" customHeight="1" s="19">
       <c r="A67" s="11" t="inlineStr">
@@ -9275,17 +9103,11 @@
       </c>
       <c r="H67" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I67" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J67" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="12" t="n"/>
     </row>
     <row r="68" ht="27.6" customHeight="1" s="19">
       <c r="A68" s="11" t="inlineStr">
@@ -9318,22 +9140,16 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H68" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I68" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J68" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="12" t="n"/>
     </row>
     <row r="69" ht="41.4" customHeight="1" s="19">
       <c r="A69" s="11" t="inlineStr">
@@ -9366,22 +9182,16 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Emilio Fuentes</t>
         </is>
       </c>
       <c r="H69" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I69" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J69" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="12" t="n"/>
     </row>
     <row r="70" ht="27.6" customHeight="1" s="19">
       <c r="A70" s="11" t="inlineStr">
@@ -9419,15 +9229,11 @@
       </c>
       <c r="H70" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I70" s="11" t="n"/>
-      <c r="J70" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J70" s="12" t="n"/>
     </row>
     <row r="71" ht="27.6" customHeight="1" s="19">
       <c r="A71" s="11" t="inlineStr">
@@ -9465,15 +9271,11 @@
       </c>
       <c r="H71" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I71" s="11" t="n"/>
-      <c r="J71" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J71" s="12" t="n"/>
     </row>
     <row r="72" ht="27.6" customHeight="1" s="19">
       <c r="A72" s="11" t="inlineStr">
@@ -9511,15 +9313,11 @@
       </c>
       <c r="H72" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I72" s="11" t="n"/>
-      <c r="J72" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J72" s="12" t="n"/>
     </row>
     <row r="73" ht="27.6" customHeight="1" s="19">
       <c r="A73" s="11" t="inlineStr">
@@ -9557,15 +9355,11 @@
       </c>
       <c r="H73" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I73" s="11" t="n"/>
-      <c r="J73" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J73" s="12" t="n"/>
     </row>
     <row r="74" ht="55.2" customHeight="1" s="19">
       <c r="A74" s="11" t="inlineStr">
@@ -9603,15 +9397,11 @@
       </c>
       <c r="H74" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I74" s="11" t="n"/>
-      <c r="J74" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J74" s="12" t="n"/>
     </row>
     <row r="75" ht="41.4" customHeight="1" s="19">
       <c r="A75" s="11" t="inlineStr">
@@ -9649,15 +9439,11 @@
       </c>
       <c r="H75" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I75" s="11" t="n"/>
-      <c r="J75" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J75" s="12" t="n"/>
     </row>
     <row r="76" ht="41.4" customHeight="1" s="19">
       <c r="A76" s="11" t="inlineStr">
@@ -9774,22 +9560,16 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H78" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I78" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J78" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="12" t="n"/>
     </row>
     <row r="79" ht="27.6" customHeight="1" s="19">
       <c r="A79" s="11" t="inlineStr">
@@ -9822,22 +9602,16 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H79" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J79" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="12" t="n"/>
     </row>
     <row r="80" ht="27.6" customHeight="1" s="19">
       <c r="A80" s="11" t="inlineStr">
@@ -9875,17 +9649,11 @@
       </c>
       <c r="H80" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I80" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J80" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="12" t="n"/>
     </row>
     <row r="81" ht="27.6" customHeight="1" s="19">
       <c r="A81" s="11" t="inlineStr">
@@ -9918,22 +9686,16 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H81" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I81" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J81" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="12" t="n"/>
     </row>
     <row r="82" ht="27.6" customHeight="1" s="19">
       <c r="A82" s="11" t="inlineStr">
@@ -9971,17 +9733,11 @@
       </c>
       <c r="H82" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I82" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J82" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I82" s="11" t="n"/>
+      <c r="J82" s="12" t="n"/>
     </row>
     <row r="83" ht="27.6" customHeight="1" s="19">
       <c r="A83" s="11" t="inlineStr">
@@ -10014,22 +9770,16 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H83" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I83" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J83" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I83" s="11" t="n"/>
+      <c r="J83" s="12" t="n"/>
     </row>
     <row r="84" ht="55.2" customHeight="1" s="19">
       <c r="A84" s="11" t="inlineStr">
@@ -10062,22 +9812,16 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H84" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I84" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J84" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="12" t="n"/>
     </row>
     <row r="85" ht="41.4" customHeight="1" s="19">
       <c r="A85" s="11" t="inlineStr">
@@ -10110,22 +9854,16 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H85" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I85" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J85" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I85" s="11" t="n"/>
+      <c r="J85" s="12" t="n"/>
     </row>
     <row r="86" ht="41.4" customHeight="1" s="19">
       <c r="A86" s="11" t="inlineStr">
@@ -10158,22 +9896,16 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H86" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I86" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J86" s="12" t="inlineStr">
-        <is>
-          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I86" s="11" t="n"/>
+      <c r="J86" s="12" t="n"/>
     </row>
     <row r="87" ht="41.4" customHeight="1" s="19">
       <c r="A87" s="11" t="inlineStr">
@@ -10206,22 +9938,16 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H87" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J87" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I87" s="11" t="n"/>
+      <c r="J87" s="12" t="n"/>
     </row>
     <row r="88" ht="41.4" customHeight="1" s="19">
       <c r="A88" s="11" t="inlineStr">
@@ -10259,17 +9985,11 @@
       </c>
       <c r="H88" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I88" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J88" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I88" s="11" t="n"/>
+      <c r="J88" s="12" t="n"/>
     </row>
     <row r="89" ht="27.6" customHeight="1" s="19">
       <c r="A89" s="11" t="inlineStr">
@@ -10302,22 +10022,16 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H89" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I89" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I89" s="11" t="n"/>
+      <c r="J89" s="12" t="n"/>
     </row>
     <row r="90" ht="27.6" customHeight="1" s="19">
       <c r="A90" s="11" t="inlineStr">
@@ -10350,22 +10064,16 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H90" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I90" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J90" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I90" s="11" t="n"/>
+      <c r="J90" s="12" t="n"/>
     </row>
     <row r="91" ht="27.6" customHeight="1" s="19">
       <c r="A91" s="11" t="inlineStr">
@@ -10398,22 +10106,16 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H91" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I91" s="11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J91" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I91" s="11" t="n"/>
+      <c r="J91" s="12" t="n"/>
     </row>
     <row r="92" ht="27.6" customHeight="1" s="19">
       <c r="A92" s="11" t="inlineStr">
@@ -10451,17 +10153,11 @@
       </c>
       <c r="H92" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I92" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="J92" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I92" s="11" t="n"/>
+      <c r="J92" s="12" t="n"/>
     </row>
     <row r="93" ht="27.6" customHeight="1" s="19">
       <c r="A93" s="11" t="inlineStr">
@@ -10494,22 +10190,16 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H93" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I93" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J93" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I93" s="11" t="n"/>
+      <c r="J93" s="12" t="n"/>
     </row>
     <row r="94" ht="55.2" customHeight="1" s="19">
       <c r="A94" s="11" t="inlineStr">
@@ -10542,22 +10232,16 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H94" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I94" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J94" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="12" t="n"/>
     </row>
     <row r="95" ht="41.4" customHeight="1" s="19">
       <c r="A95" s="11" t="inlineStr">
@@ -10590,22 +10274,16 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>Catalina Pescio</t>
+          <t>Bryan Chávez</t>
         </is>
       </c>
       <c r="H95" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I95" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J95" s="12" t="inlineStr">
-        <is>
-          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="12" t="n"/>
     </row>
     <row r="96" ht="41.4" customHeight="1" s="19">
       <c r="A96" s="11" t="inlineStr">
@@ -10638,22 +10316,16 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H96" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I96" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J96" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="12" t="n"/>
     </row>
     <row r="97" ht="27.6" customHeight="1" s="19">
       <c r="A97" s="11" t="inlineStr">
@@ -10686,22 +10358,16 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H97" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I97" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J97" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I97" s="11" t="n"/>
+      <c r="J97" s="12" t="n"/>
     </row>
     <row r="98" ht="41.4" customHeight="1" s="19">
       <c r="A98" s="11" t="inlineStr">
@@ -10739,17 +10405,11 @@
       </c>
       <c r="H98" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I98" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J98" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I98" s="11" t="n"/>
+      <c r="J98" s="12" t="n"/>
     </row>
     <row r="99" ht="41.4" customHeight="1" s="19">
       <c r="A99" s="11" t="inlineStr">
@@ -10782,22 +10442,16 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H99" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I99" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J99" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I99" s="11" t="n"/>
+      <c r="J99" s="12" t="n"/>
     </row>
     <row r="100" ht="27.6" customHeight="1" s="19">
       <c r="A100" s="11" t="inlineStr">
@@ -10830,22 +10484,16 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H100" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I100" s="11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J100" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I100" s="11" t="n"/>
+      <c r="J100" s="12" t="n"/>
     </row>
     <row r="101" ht="27.6" customHeight="1" s="19">
       <c r="A101" s="11" t="inlineStr">
@@ -10878,22 +10526,16 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H101" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I101" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="J101" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="12" t="n"/>
     </row>
     <row r="102" ht="27.6" customHeight="1" s="19">
       <c r="A102" s="11" t="inlineStr">
@@ -10926,22 +10568,16 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H102" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I102" s="11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="J102" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="12" t="n"/>
     </row>
     <row r="103" ht="27.6" customHeight="1" s="19">
       <c r="A103" s="11" t="inlineStr">
@@ -10979,17 +10615,11 @@
       </c>
       <c r="H103" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I103" s="11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="J103" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="12" t="n"/>
     </row>
     <row r="104" ht="27.6" customHeight="1" s="19">
       <c r="A104" s="11" t="inlineStr">
@@ -11027,17 +10657,11 @@
       </c>
       <c r="H104" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I104" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J104" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="12" t="n"/>
     </row>
     <row r="105" ht="55.2" customHeight="1" s="19">
       <c r="A105" s="11" t="inlineStr">
@@ -11075,17 +10699,11 @@
       </c>
       <c r="H105" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I105" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J105" s="12" t="inlineStr">
-        <is>
-          <t>Validación con la Product Owner registrada conforme (17-10-2026).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="12" t="n"/>
     </row>
     <row r="106" ht="41.4" customHeight="1" s="19">
       <c r="A106" s="11" t="inlineStr">
@@ -11123,15 +10741,11 @@
       </c>
       <c r="H106" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I106" s="11" t="n"/>
-      <c r="J106" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J106" s="12" t="n"/>
     </row>
     <row r="107" ht="41.4" customHeight="1" s="19">
       <c r="A107" s="11" t="inlineStr">
@@ -11169,15 +10783,11 @@
       </c>
       <c r="H107" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I107" s="11" t="n"/>
-      <c r="J107" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J107" s="12" t="n"/>
     </row>
     <row r="108" ht="27.6" customHeight="1" s="19">
       <c r="A108" s="11" t="inlineStr">
@@ -11215,15 +10825,11 @@
       </c>
       <c r="H108" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I108" s="11" t="n"/>
-      <c r="J108" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J108" s="12" t="n"/>
     </row>
     <row r="109" ht="41.4" customHeight="1" s="19">
       <c r="A109" s="11" t="inlineStr">
@@ -11261,15 +10867,11 @@
       </c>
       <c r="H109" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I109" s="11" t="n"/>
-      <c r="J109" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J109" s="12" t="n"/>
     </row>
     <row r="110" ht="41.4" customHeight="1" s="19">
       <c r="A110" s="11" t="inlineStr">
@@ -11391,15 +10993,11 @@
       </c>
       <c r="H112" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I112" s="11" t="n"/>
-      <c r="J112" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J112" s="12" t="n"/>
     </row>
     <row r="113" ht="27.6" customHeight="1" s="19">
       <c r="A113" s="11" t="inlineStr">
@@ -11479,15 +11077,11 @@
       </c>
       <c r="H114" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I114" s="11" t="n"/>
-      <c r="J114" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J114" s="12" t="n"/>
     </row>
     <row r="115" ht="27.6" customHeight="1" s="19">
       <c r="A115" s="11" t="inlineStr">
@@ -11609,15 +11203,11 @@
       </c>
       <c r="H117" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I117" s="11" t="n"/>
-      <c r="J117" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J117" s="12" t="n"/>
     </row>
     <row r="118" ht="41.4" customHeight="1" s="19">
       <c r="A118" s="11" t="inlineStr">
@@ -11655,15 +11245,11 @@
       </c>
       <c r="H118" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I118" s="11" t="n"/>
-      <c r="J118" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J118" s="12" t="n"/>
     </row>
     <row r="119" ht="41.4" customHeight="1" s="19">
       <c r="A119" s="11" t="inlineStr">
@@ -11701,15 +11287,11 @@
       </c>
       <c r="H119" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I119" s="11" t="n"/>
-      <c r="J119" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J119" s="12" t="n"/>
     </row>
     <row r="120" ht="27.6" customHeight="1" s="19">
       <c r="A120" s="11" t="inlineStr">
@@ -11747,15 +11329,11 @@
       </c>
       <c r="H120" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I120" s="11" t="n"/>
-      <c r="J120" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J120" s="12" t="n"/>
     </row>
     <row r="121" ht="27.6" customHeight="1" s="19">
       <c r="A121" s="11" t="inlineStr">
@@ -11793,15 +11371,11 @@
       </c>
       <c r="H121" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I121" s="11" t="n"/>
-      <c r="J121" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J121" s="12" t="n"/>
     </row>
     <row r="122" ht="41.4" customHeight="1" s="19">
       <c r="A122" s="11" t="inlineStr">
@@ -11839,15 +11413,11 @@
       </c>
       <c r="H122" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I122" s="11" t="n"/>
-      <c r="J122" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J122" s="12" t="n"/>
     </row>
     <row r="123" ht="27.6" customHeight="1" s="19">
       <c r="A123" s="11" t="inlineStr">
@@ -11885,15 +11455,11 @@
       </c>
       <c r="H123" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I123" s="11" t="n"/>
-      <c r="J123" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J123" s="12" t="n"/>
     </row>
     <row r="124" ht="27.6" customHeight="1" s="19">
       <c r="A124" s="11" t="inlineStr">
@@ -12057,15 +11623,11 @@
       </c>
       <c r="H127" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I127" s="11" t="n"/>
-      <c r="J127" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J127" s="12" t="n"/>
     </row>
     <row r="128" ht="41.4" customHeight="1" s="19">
       <c r="A128" s="11" t="inlineStr">
@@ -12103,15 +11665,11 @@
       </c>
       <c r="H128" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I128" s="11" t="n"/>
-      <c r="J128" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J128" s="12" t="n"/>
     </row>
     <row r="129" ht="55.2" customHeight="1" s="19">
       <c r="A129" s="11" t="inlineStr">
@@ -12149,15 +11707,11 @@
       </c>
       <c r="H129" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I129" s="11" t="n"/>
-      <c r="J129" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J129" s="12" t="n"/>
     </row>
     <row r="130" ht="41.4" customHeight="1" s="19">
       <c r="A130" s="11" t="inlineStr">
@@ -12195,15 +11749,11 @@
       </c>
       <c r="H130" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I130" s="11" t="n"/>
-      <c r="J130" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J130" s="12" t="n"/>
     </row>
     <row r="131" ht="41.4" customHeight="1" s="19">
       <c r="A131" s="11" t="inlineStr">
@@ -12241,15 +11791,11 @@
       </c>
       <c r="H131" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I131" s="11" t="n"/>
-      <c r="J131" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J131" s="12" t="n"/>
     </row>
     <row r="132" ht="41.4" customHeight="1" s="19">
       <c r="A132" s="11" t="inlineStr">
@@ -12287,15 +11833,11 @@
       </c>
       <c r="H132" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I132" s="11" t="n"/>
-      <c r="J132" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J132" s="12" t="n"/>
     </row>
     <row r="133" ht="41.4" customHeight="1" s="19">
       <c r="A133" s="11" t="inlineStr">
@@ -12333,15 +11875,11 @@
       </c>
       <c r="H133" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I133" s="11" t="n"/>
-      <c r="J133" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción web asociada al 16-10-2026; ver la observación de la historia. Falta confirmar contra esta tarea.</t>
-        </is>
-      </c>
+      <c r="J133" s="12" t="n"/>
     </row>
     <row r="134" ht="27.6" customHeight="1" s="19">
       <c r="A134" s="11" t="inlineStr">
@@ -12589,7 +12127,7 @@
       </c>
       <c r="H139" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I139" s="11" t="n">
@@ -12847,7 +12385,7 @@
       </c>
       <c r="H145" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I145" s="11" t="n">
@@ -13155,7 +12693,7 @@
       </c>
       <c r="H152" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I152" s="11" t="n">
@@ -13341,7 +12879,7 @@
       </c>
       <c r="H156" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I156" s="11" t="n">
@@ -13733,7 +13271,7 @@
       </c>
       <c r="H165" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I165" s="11" t="n">
@@ -13873,7 +13411,7 @@
       </c>
       <c r="H168" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I168" s="11" t="n">
@@ -13967,7 +13505,7 @@
       </c>
       <c r="H170" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I170" s="11" t="n">
@@ -14183,15 +13721,11 @@
       </c>
       <c r="H175" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I175" s="11" t="n"/>
-      <c r="J175" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J175" s="12" t="n"/>
     </row>
     <row r="176" ht="27.6" customHeight="1" s="19">
       <c r="A176" s="11" t="inlineStr">
@@ -14229,15 +13763,11 @@
       </c>
       <c r="H176" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I176" s="11" t="n"/>
-      <c r="J176" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J176" s="12" t="n"/>
     </row>
     <row r="177" ht="27.6" customHeight="1" s="19">
       <c r="A177" s="11" t="inlineStr">
@@ -14275,15 +13805,11 @@
       </c>
       <c r="H177" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I177" s="11" t="n"/>
-      <c r="J177" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J177" s="12" t="n"/>
     </row>
     <row r="178" ht="27.6" customHeight="1" s="19">
       <c r="A178" s="11" t="inlineStr">
@@ -14321,15 +13847,11 @@
       </c>
       <c r="H178" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I178" s="11" t="n"/>
-      <c r="J178" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J178" s="12" t="n"/>
     </row>
     <row r="179" ht="27.6" customHeight="1" s="19">
       <c r="A179" s="11" t="inlineStr">
@@ -14367,15 +13889,11 @@
       </c>
       <c r="H179" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I179" s="11" t="n"/>
-      <c r="J179" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J179" s="12" t="n"/>
     </row>
     <row r="180" ht="41.4" customHeight="1" s="19">
       <c r="A180" s="11" t="inlineStr">
@@ -14413,15 +13931,11 @@
       </c>
       <c r="H180" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I180" s="11" t="n"/>
-      <c r="J180" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J180" s="12" t="n"/>
     </row>
     <row r="181" ht="55.2" customHeight="1" s="19">
       <c r="A181" s="11" t="inlineStr">
@@ -14459,15 +13973,11 @@
       </c>
       <c r="H181" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I181" s="11" t="n"/>
-      <c r="J181" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J181" s="12" t="n"/>
     </row>
     <row r="182" ht="41.4" customHeight="1" s="19">
       <c r="A182" s="11" t="inlineStr">
@@ -14589,15 +14099,11 @@
       </c>
       <c r="H184" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I184" s="11" t="n"/>
-      <c r="J184" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J184" s="12" t="n"/>
     </row>
     <row r="185" ht="41.4" customHeight="1" s="19">
       <c r="A185" s="11" t="inlineStr">
@@ -14635,15 +14141,11 @@
       </c>
       <c r="H185" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I185" s="11" t="n"/>
-      <c r="J185" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J185" s="12" t="n"/>
     </row>
     <row r="186" ht="41.4" customHeight="1" s="19">
       <c r="A186" s="11" t="inlineStr">
@@ -14681,15 +14183,11 @@
       </c>
       <c r="H186" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I186" s="11" t="n"/>
-      <c r="J186" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J186" s="12" t="n"/>
     </row>
     <row r="187" ht="27.6" customHeight="1" s="19">
       <c r="A187" s="11" t="inlineStr">
@@ -14727,15 +14225,11 @@
       </c>
       <c r="H187" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I187" s="11" t="n"/>
-      <c r="J187" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J187" s="12" t="n"/>
     </row>
     <row r="188" ht="27.6" customHeight="1" s="19">
       <c r="A188" s="11" t="inlineStr">
@@ -14773,15 +14267,11 @@
       </c>
       <c r="H188" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I188" s="11" t="n"/>
-      <c r="J188" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J188" s="12" t="n"/>
     </row>
     <row r="189" ht="27.6" customHeight="1" s="19">
       <c r="A189" s="11" t="inlineStr">
@@ -14819,15 +14309,11 @@
       </c>
       <c r="H189" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I189" s="11" t="n"/>
-      <c r="J189" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J189" s="12" t="n"/>
     </row>
     <row r="190" ht="27.6" customHeight="1" s="19">
       <c r="A190" s="11" t="inlineStr">
@@ -14991,15 +14477,11 @@
       </c>
       <c r="H193" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I193" s="11" t="n"/>
-      <c r="J193" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J193" s="12" t="n"/>
     </row>
     <row r="194" ht="41.4" customHeight="1" s="19">
       <c r="A194" s="11" t="inlineStr">
@@ -15037,15 +14519,11 @@
       </c>
       <c r="H194" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I194" s="11" t="n"/>
-      <c r="J194" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J194" s="12" t="n"/>
     </row>
     <row r="195" ht="41.4" customHeight="1" s="19">
       <c r="A195" s="11" t="inlineStr">
@@ -15083,15 +14561,11 @@
       </c>
       <c r="H195" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I195" s="11" t="n"/>
-      <c r="J195" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J195" s="12" t="n"/>
     </row>
     <row r="196" ht="27.6" customHeight="1" s="19">
       <c r="A196" s="11" t="inlineStr">
@@ -15129,15 +14603,11 @@
       </c>
       <c r="H196" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I196" s="11" t="n"/>
-      <c r="J196" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J196" s="12" t="n"/>
     </row>
     <row r="197" ht="41.4" customHeight="1" s="19">
       <c r="A197" s="11" t="inlineStr">
@@ -15175,15 +14645,11 @@
       </c>
       <c r="H197" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I197" s="11" t="n"/>
-      <c r="J197" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J197" s="12" t="n"/>
     </row>
     <row r="198" ht="41.4" customHeight="1" s="19">
       <c r="A198" s="11" t="inlineStr">
@@ -15221,15 +14687,11 @@
       </c>
       <c r="H198" s="11" t="inlineStr">
         <is>
-          <t>En revisión</t>
+          <t>Por hacer</t>
         </is>
       </c>
       <c r="I198" s="11" t="n"/>
-      <c r="J198" s="12" t="inlineStr">
-        <is>
-          <t>Hay construcción asociada al 17-10-2026; ver la observación de la historia.</t>
-        </is>
-      </c>
+      <c r="J198" s="12" t="n"/>
     </row>
     <row r="199" ht="27.6" customHeight="1" s="19">
       <c r="A199" s="11" t="inlineStr">
@@ -15388,22 +14850,16 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H202" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I202" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J202" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I202" s="11" t="n"/>
+      <c r="J202" s="12" t="n"/>
     </row>
     <row r="203" ht="27.6" customHeight="1" s="19">
       <c r="A203" s="11" t="inlineStr">
@@ -15436,22 +14892,16 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H203" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I203" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J203" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I203" s="11" t="n"/>
+      <c r="J203" s="12" t="n"/>
     </row>
     <row r="204" ht="41.4" customHeight="1" s="19">
       <c r="A204" s="11" t="inlineStr">
@@ -15489,17 +14939,11 @@
       </c>
       <c r="H204" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I204" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J204" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I204" s="11" t="n"/>
+      <c r="J204" s="12" t="n"/>
     </row>
     <row r="205" ht="55.2" customHeight="1" s="19">
       <c r="A205" s="11" t="inlineStr">
@@ -15532,22 +14976,16 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H205" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I205" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J205" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I205" s="11" t="n"/>
+      <c r="J205" s="12" t="n"/>
     </row>
     <row r="206" ht="41.4" customHeight="1" s="19">
       <c r="A206" s="11" t="inlineStr">
@@ -15580,22 +15018,16 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>Bryan Chávez</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H206" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I206" s="11" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="J206" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I206" s="11" t="n"/>
+      <c r="J206" s="12" t="n"/>
     </row>
     <row r="207" ht="41.4" customHeight="1" s="19">
       <c r="A207" s="11" t="inlineStr">
@@ -15628,22 +15060,16 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>Emilio Fuentes</t>
+          <t>Catalina Pescio</t>
         </is>
       </c>
       <c r="H207" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I207" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J207" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I207" s="11" t="n"/>
+      <c r="J207" s="12" t="n"/>
     </row>
     <row r="208" ht="41.4" customHeight="1" s="19">
       <c r="A208" s="11" t="inlineStr">
@@ -15681,17 +15107,11 @@
       </c>
       <c r="H208" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I208" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="J208" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I208" s="11" t="n"/>
+      <c r="J208" s="12" t="n"/>
     </row>
     <row r="209" ht="41.4" customHeight="1" s="19">
       <c r="A209" s="11" t="inlineStr">
@@ -15729,17 +15149,11 @@
       </c>
       <c r="H209" s="11" t="inlineStr">
         <is>
-          <t>Terminada</t>
-        </is>
-      </c>
-      <c r="I209" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J209" s="12" t="inlineStr">
-        <is>
-          <t>Cubierta por lo construido el 17-10-2026 (ver la observación de la historia).</t>
-        </is>
-      </c>
+          <t>Por hacer</t>
+        </is>
+      </c>
+      <c r="I209" s="11" t="n"/>
+      <c r="J209" s="12" t="n"/>
     </row>
     <row r="210" ht="27.6" customHeight="1" s="19">
       <c r="A210" s="11" t="inlineStr">
@@ -30553,7 +29967,7 @@
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30584,7 +29998,7 @@
       </c>
       <c r="F20" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30615,7 +30029,7 @@
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30876,7 +30290,7 @@
       </c>
       <c r="F29" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30911,7 +30325,7 @@
       </c>
       <c r="F30" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30942,7 +30356,7 @@
       </c>
       <c r="F31" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -30974,7 +30388,7 @@
       </c>
       <c r="F32" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31036,7 +30450,7 @@
       </c>
       <c r="F34" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31068,7 +30482,7 @@
       </c>
       <c r="F35" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31100,7 +30514,7 @@
       </c>
       <c r="F36" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31131,7 +30545,7 @@
       </c>
       <c r="F37" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31163,7 +30577,7 @@
       </c>
       <c r="F38" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31194,7 +30608,7 @@
       </c>
       <c r="F39" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31225,7 +30639,7 @@
       </c>
       <c r="F40" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31257,7 +30671,7 @@
       </c>
       <c r="F41" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31288,7 +30702,7 @@
       </c>
       <c r="F42" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31320,7 +30734,7 @@
       </c>
       <c r="F43" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31351,7 +30765,7 @@
       </c>
       <c r="F44" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31383,7 +30797,7 @@
       </c>
       <c r="F45" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31446,7 +30860,7 @@
       </c>
       <c r="F47" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31478,7 +30892,7 @@
       </c>
       <c r="F48" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31573,7 +30987,7 @@
       </c>
       <c r="F51" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31605,7 +31019,7 @@
       </c>
       <c r="F52" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31668,7 +31082,7 @@
       </c>
       <c r="F54" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -31985,7 +31399,7 @@
       </c>
       <c r="F64" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32016,7 +31430,7 @@
       </c>
       <c r="F65" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32111,7 +31525,7 @@
       </c>
       <c r="F68" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32142,7 +31556,7 @@
       </c>
       <c r="F69" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32174,7 +31588,7 @@
       </c>
       <c r="F70" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32205,7 +31619,7 @@
       </c>
       <c r="F71" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32267,7 +31681,7 @@
       </c>
       <c r="F73" s="13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -32298,7 +31712,7 @@
       </c>
       <c r="F74" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
